--- a/PROTOPUS/PROTOPUS_Baker_Mixer_BOM_and_Costing.xlsx
+++ b/PROTOPUS/PROTOPUS_Baker_Mixer_BOM_and_Costing.xlsx
@@ -149,7 +149,7 @@
     <t xml:space="preserve">Founder stipend per month</t>
   </si>
   <si>
-    <t xml:space="preserve">ASSUMPTION: modest living stipend; set to 0 if the funder does not allow it</t>
+    <t xml:space="preserve">Deducted: the founder takes no stipend during the proof of concept</t>
   </si>
   <si>
     <t xml:space="preserve">Proto software + compute per month</t>
@@ -2201,11 +2201,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="33627937"/>
-        <c:axId val="25503896"/>
+        <c:axId val="19349946"/>
+        <c:axId val="25974372"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="33627937"/>
+        <c:axId val="19349946"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2237,7 +2237,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="25503896"/>
+        <c:crossAx val="25974372"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2245,7 +2245,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="25503896"/>
+        <c:axId val="25974372"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2287,7 +2287,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="33627937"/>
+        <c:crossAx val="19349946"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2515,11 +2515,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="53678661"/>
-        <c:axId val="20665165"/>
+        <c:axId val="80062474"/>
+        <c:axId val="71721433"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="53678661"/>
+        <c:axId val="80062474"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -2551,7 +2551,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="20665165"/>
+        <c:crossAx val="71721433"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2559,7 +2559,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="20665165"/>
+        <c:axId val="71721433"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2591,7 +2591,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="53678661"/>
+        <c:crossAx val="80062474"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2759,11 +2759,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="30302956"/>
-        <c:axId val="30836831"/>
+        <c:axId val="71780562"/>
+        <c:axId val="90186796"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="30302956"/>
+        <c:axId val="71780562"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -2795,7 +2795,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="30836831"/>
+        <c:crossAx val="90186796"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2803,7 +2803,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="30836831"/>
+        <c:axId val="90186796"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2835,7 +2835,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="30302956"/>
+        <c:crossAx val="71780562"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4109,7 +4109,7 @@
         <v>36</v>
       </c>
       <c r="B9" s="19" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="C9" s="18" t="s">
         <v>37</v>
@@ -4270,7 +4270,7 @@
       </c>
       <c r="B21" s="7" t="n">
         <f aca="false">$B$9*$B$6</f>
-        <v>180000</v>
+        <v>0</v>
       </c>
       <c r="C21" s="16" t="s">
         <v>63</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="B27" s="23" t="n">
         <f aca="false">SUM(B15:B26)</f>
-        <v>1978264.8756</v>
+        <v>1798264.8756</v>
       </c>
       <c r="C27" s="24"/>
       <c r="D27" s="24"/>
@@ -4385,7 +4385,7 @@
       </c>
       <c r="B28" s="25" t="n">
         <f aca="false">SUMIF(E15:E26,"N",B15:B26)</f>
-        <v>1530000</v>
+        <v>1350000</v>
       </c>
       <c r="C28" s="24"/>
       <c r="D28" s="24"/>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="B29" s="27" t="n">
         <f aca="false">ROUND((B27+B28*$B$11)/100000,0)*100000</f>
-        <v>2100000</v>
+        <v>1900000</v>
       </c>
       <c r="C29" s="28"/>
       <c r="D29" s="28"/>
@@ -4407,11 +4407,11 @@
       </c>
       <c r="B30" s="25" t="n">
         <f aca="false">B29-B27</f>
-        <v>121735.1244</v>
+        <v>101735.1244</v>
       </c>
       <c r="C30" s="29" t="n">
         <f aca="false">IF(B28=0,0,B30/B28)</f>
-        <v>0.0795654407843138</v>
+        <v>0.0753593514074075</v>
       </c>
       <c r="D30" s="18" t="s">
         <v>84</v>
@@ -4443,7 +4443,7 @@
       </c>
       <c r="C34" s="30" t="n">
         <f aca="false">IF($B$29=0,0,B34/$B$29)</f>
-        <v>0.213459464571429</v>
+        <v>0.235928881894737</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4456,7 +4456,7 @@
       </c>
       <c r="C35" s="30" t="n">
         <f aca="false">IF($B$29=0,0,B35/$B$29)</f>
-        <v>0.104761904761905</v>
+        <v>0.115789473684211</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4465,11 +4465,11 @@
       </c>
       <c r="B36" s="7" t="n">
         <f aca="false">SUMIF($C$15:$C$26,A36,$B$15:$B$26)</f>
-        <v>900000</v>
+        <v>720000</v>
       </c>
       <c r="C36" s="30" t="n">
         <f aca="false">IF($B$29=0,0,B36/$B$29)</f>
-        <v>0.428571428571429</v>
+        <v>0.378947368421053</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="C37" s="30" t="n">
         <f aca="false">IF($B$29=0,0,B37/$B$29)</f>
-        <v>0.0642857142857143</v>
+        <v>0.0710526315789474</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4495,7 +4495,7 @@
       </c>
       <c r="C38" s="30" t="n">
         <f aca="false">IF($B$29=0,0,B38/$B$29)</f>
-        <v>0.0714285714285714</v>
+        <v>0.0789473684210526</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4504,11 +4504,11 @@
       </c>
       <c r="B39" s="7" t="n">
         <f aca="false">SUMIF($C$15:$C$26,A39,$B$15:$B$26)+B30</f>
-        <v>246735.1244</v>
+        <v>226735.1244</v>
       </c>
       <c r="C39" s="30" t="n">
         <f aca="false">IF($B$29=0,0,B39/$B$29)</f>
-        <v>0.117492916380952</v>
+        <v>0.119334276</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="B45" s="34" t="n">
         <f aca="false">B29</f>
-        <v>2100000</v>
+        <v>1900000</v>
       </c>
       <c r="C45" s="28" t="str">
         <f aca="false">B6&amp;" months"</f>
@@ -4575,7 +4575,7 @@
       </c>
       <c r="B46" s="7" t="n">
         <f aca="false">ROUND((B29+'Baker Final Cost'!B10+$B$8*$B$6+250000)/100000,0)*100000</f>
-        <v>3100000</v>
+        <v>2900000</v>
       </c>
       <c r="C46" s="24" t="str">
         <f aca="false">B6&amp;" months"</f>

--- a/PROTOPUS/PROTOPUS_Baker_Mixer_BOM_and_Costing.xlsx
+++ b/PROTOPUS/PROTOPUS_Baker_Mixer_BOM_and_Costing.xlsx
@@ -134,16 +134,16 @@
     <t xml:space="preserve">6 months to proof of concept (deck timeline) + 3 months to close the next round</t>
   </si>
   <si>
-    <t xml:space="preserve">Engineers (firmware + mechanical)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deck: hiring next, a firmware engineer and a mechanical engineer</t>
+    <t xml:space="preserve">Engineers (software + firmware)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One software engineer who also writes the firmware; the founder covers mechanical and electronics</t>
   </si>
   <si>
     <t xml:space="preserve">Cost per engineer per month</t>
   </si>
   <si>
-    <t xml:space="preserve">ASSUMPTION: entry-level embedded/mechanical engineer in Delhi; the ₹10L ask assumed ₹25,000</t>
+    <t xml:space="preserve">ASSUMPTION: software + firmware in one person, Delhi; ₹40,000 would lower the ask to ₹15L. The ₹10L ask assumed ₹25,000</t>
   </si>
   <si>
     <t xml:space="preserve">Founder stipend per month</t>
@@ -335,10 +335,10 @@
     <t xml:space="preserve">Too early</t>
   </si>
   <si>
-    <t xml:space="preserve">Adds a second Baker for a studio, a third engineer and China samples + trip. That is seed-round work: it spends money before the PoC has removed the risk.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Too-early option adds: second Baker at prototype cost, one more engineer for the runway, ₹2,50,000 for China DFM samples + one Shenzhen trip (ASSUMPTION).</t>
+    <t xml:space="preserve">Adds a second Baker for a studio, a mechanical engineer and China samples + trip. That is seed-round work: it spends money before the PoC has removed the risk.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Too-early option adds: second Baker at prototype cost, one more engineer (mechanical) for the runway, ₹2,50,000 for China DFM samples + one Shenzhen trip (ASSUMPTION).</t>
   </si>
   <si>
     <t xml:space="preserve">Baker — prototype bill of materials (India-sourced)</t>
@@ -2201,11 +2201,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="19349946"/>
-        <c:axId val="25974372"/>
+        <c:axId val="95840242"/>
+        <c:axId val="31076756"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="19349946"/>
+        <c:axId val="95840242"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2237,7 +2237,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="25974372"/>
+        <c:crossAx val="31076756"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2245,7 +2245,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="25974372"/>
+        <c:axId val="31076756"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2287,7 +2287,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="19349946"/>
+        <c:crossAx val="95840242"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2515,11 +2515,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="80062474"/>
-        <c:axId val="71721433"/>
+        <c:axId val="69033556"/>
+        <c:axId val="49193885"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="80062474"/>
+        <c:axId val="69033556"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -2551,7 +2551,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="71721433"/>
+        <c:crossAx val="49193885"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2559,7 +2559,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="71721433"/>
+        <c:axId val="49193885"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2591,7 +2591,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="80062474"/>
+        <c:crossAx val="69033556"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2759,11 +2759,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="71780562"/>
-        <c:axId val="90186796"/>
+        <c:axId val="47919889"/>
+        <c:axId val="23178642"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="71780562"/>
+        <c:axId val="47919889"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -2795,7 +2795,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90186796"/>
+        <c:crossAx val="23178642"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2803,7 +2803,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="90186796"/>
+        <c:axId val="23178642"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2835,7 +2835,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="71780562"/>
+        <c:crossAx val="47919889"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4087,7 +4087,7 @@
         <v>32</v>
       </c>
       <c r="B7" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" s="18" t="s">
         <v>33</v>
@@ -4098,7 +4098,7 @@
         <v>34</v>
       </c>
       <c r="B8" s="19" t="n">
-        <v>40000</v>
+        <v>50000</v>
       </c>
       <c r="C8" s="18" t="s">
         <v>35</v>
@@ -4252,7 +4252,7 @@
       </c>
       <c r="B20" s="7" t="n">
         <f aca="false">$B$7*$B$8*$B$6</f>
-        <v>720000</v>
+        <v>450000</v>
       </c>
       <c r="C20" s="16" t="s">
         <v>63</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="B27" s="23" t="n">
         <f aca="false">SUM(B15:B26)</f>
-        <v>1798264.8756</v>
+        <v>1528264.8756</v>
       </c>
       <c r="C27" s="24"/>
       <c r="D27" s="24"/>
@@ -4385,7 +4385,7 @@
       </c>
       <c r="B28" s="25" t="n">
         <f aca="false">SUMIF(E15:E26,"N",B15:B26)</f>
-        <v>1350000</v>
+        <v>1080000</v>
       </c>
       <c r="C28" s="24"/>
       <c r="D28" s="24"/>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="B29" s="27" t="n">
         <f aca="false">ROUND((B27+B28*$B$11)/100000,0)*100000</f>
-        <v>1900000</v>
+        <v>1600000</v>
       </c>
       <c r="C29" s="28"/>
       <c r="D29" s="28"/>
@@ -4407,11 +4407,11 @@
       </c>
       <c r="B30" s="25" t="n">
         <f aca="false">B29-B27</f>
-        <v>101735.1244</v>
+        <v>71735.1244000001</v>
       </c>
       <c r="C30" s="29" t="n">
         <f aca="false">IF(B28=0,0,B30/B28)</f>
-        <v>0.0753593514074075</v>
+        <v>0.0664214114814816</v>
       </c>
       <c r="D30" s="18" t="s">
         <v>84</v>
@@ -4443,7 +4443,7 @@
       </c>
       <c r="C34" s="30" t="n">
         <f aca="false">IF($B$29=0,0,B34/$B$29)</f>
-        <v>0.235928881894737</v>
+        <v>0.28016554725</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4456,7 +4456,7 @@
       </c>
       <c r="C35" s="30" t="n">
         <f aca="false">IF($B$29=0,0,B35/$B$29)</f>
-        <v>0.115789473684211</v>
+        <v>0.1375</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4465,11 +4465,11 @@
       </c>
       <c r="B36" s="7" t="n">
         <f aca="false">SUMIF($C$15:$C$26,A36,$B$15:$B$26)</f>
-        <v>720000</v>
+        <v>450000</v>
       </c>
       <c r="C36" s="30" t="n">
         <f aca="false">IF($B$29=0,0,B36/$B$29)</f>
-        <v>0.378947368421053</v>
+        <v>0.28125</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="C37" s="30" t="n">
         <f aca="false">IF($B$29=0,0,B37/$B$29)</f>
-        <v>0.0710526315789474</v>
+        <v>0.084375</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4495,7 +4495,7 @@
       </c>
       <c r="C38" s="30" t="n">
         <f aca="false">IF($B$29=0,0,B38/$B$29)</f>
-        <v>0.0789473684210526</v>
+        <v>0.09375</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4504,11 +4504,11 @@
       </c>
       <c r="B39" s="7" t="n">
         <f aca="false">SUMIF($C$15:$C$26,A39,$B$15:$B$26)+B30</f>
-        <v>226735.1244</v>
+        <v>196735.1244</v>
       </c>
       <c r="C39" s="30" t="n">
         <f aca="false">IF($B$29=0,0,B39/$B$29)</f>
-        <v>0.119334276</v>
+        <v>0.12295945275</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="B45" s="34" t="n">
         <f aca="false">B29</f>
-        <v>1900000</v>
+        <v>1600000</v>
       </c>
       <c r="C45" s="28" t="str">
         <f aca="false">B6&amp;" months"</f>
@@ -4575,7 +4575,7 @@
       </c>
       <c r="B46" s="7" t="n">
         <f aca="false">ROUND((B29+'Baker Final Cost'!B10+$B$8*$B$6+250000)/100000,0)*100000</f>
-        <v>2900000</v>
+        <v>2700000</v>
       </c>
       <c r="C46" s="24" t="str">
         <f aca="false">B6&amp;" months"</f>

--- a/PROTOPUS/PROTOPUS_Baker_Mixer_BOM_and_Costing.xlsx
+++ b/PROTOPUS/PROTOPUS_Baker_Mixer_BOM_and_Costing.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1158" uniqueCount="436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1150" uniqueCount="432">
   <si>
     <t xml:space="preserve">PROTOPUS — Baker + Mixer: BOM, cost breakup and final cost</t>
   </si>
@@ -110,7 +110,7 @@
     <t xml:space="preserve">7. Jig printing on Baker’s own UV engine (production) replaces the separate resin printer and is flagged for testing.</t>
   </si>
   <si>
-    <t xml:space="preserve">PROTOPUS — proof-of-concept budget (the ask)</t>
+    <t xml:space="preserve">PROTOPUS — proof-of-concept budget (the ask): Baker first</t>
   </si>
   <si>
     <t xml:space="preserve">Blue = inputs you can change. The total rounds to the nearest lakh; the reserve is whatever the rounding leaves. Hardware lines link to the cost sheets.</t>
@@ -194,12 +194,6 @@
     <t xml:space="preserve">Y</t>
   </si>
   <si>
-    <t xml:space="preserve">Mixer prototype build</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Costed BOM, 26 lines, incl. duty + 15% contingency</t>
-  </si>
-  <si>
     <t xml:space="preserve">Baker Rev B iteration (heads, fixture, film module, wiring)</t>
   </si>
   <si>
@@ -212,12 +206,6 @@
     <t xml:space="preserve">N</t>
   </si>
   <si>
-    <t xml:space="preserve">Mixer production board Rev A, 5 units (8-bit design)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASSUMPTION: 5 × ~₹9,900 parts (cost report) + small-batch PCBA, stencil, courier. Units double as maker-studio demo units</t>
-  </si>
-  <si>
     <t xml:space="preserve">PoC consumables (~150 test boards)</t>
   </si>
   <si>
@@ -317,28 +305,28 @@
     <t xml:space="preserve">What it buys / why not</t>
   </si>
   <si>
-    <t xml:space="preserve">Lean (the old ask)</t>
+    <t xml:space="preserve">Lean (if the round is capped at ₹10L)</t>
   </si>
   <si>
     <t xml:space="preserve">6 months</t>
   </si>
   <si>
-    <t xml:space="preserve">One build, engineers at ₹25,000/month, no iteration money, no reserve. Runway ends exactly at PoC: no time to raise, and one failed process point stops the project.</t>
+    <t xml:space="preserve">Baker build ₹3.73L + Rev B ₹1.0L + engineer 6 months ₹3.0L + compute ₹0.9L + testing ₹1.0L = ₹9.63L. Defers lab set-up, IP, outreach; little reserve; fundraising must start at month 4.</t>
   </si>
   <si>
     <t xml:space="preserve">Comfortable (recommended)</t>
   </si>
   <si>
-    <t xml:space="preserve">Build, fix, prove, raise: market salaries, Baker Rev B, 5 production Mixer boards as studio units, IP filed, reserve, 3 months to close the next round.</t>
+    <t xml:space="preserve">Build, fix, prove, raise: one engineer at market salary, Baker Rev B, ~150 test boards, lab safety, IP filed, outreach, reserve, 3 months to close the next round.</t>
   </si>
   <si>
     <t xml:space="preserve">Too early</t>
   </si>
   <si>
-    <t xml:space="preserve">Adds a second Baker for a studio, a mechanical engineer and China samples + trip. That is seed-round work: it spends money before the PoC has removed the risk.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Too-early option adds: second Baker at prototype cost, one more engineer (mechanical) for the runway, ₹2,50,000 for China DFM samples + one Shenzhen trip (ASSUMPTION).</t>
+    <t xml:space="preserve">Adds Mixer now (prototype + 5 boards), a second Baker for a studio, a mechanical engineer and China samples + trip. Two products at once: that is seed-round work.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Too-early option adds: Mixer prototype + 5 production Mixer boards (₹60,000), a second Baker at prototype cost, a mechanical engineer for the runway, ₹2,50,000 for China samples + one Shenzhen trip (ASSUMPTION). Mixer is Step 2, funded after the PoC.</t>
   </si>
   <si>
     <t xml:space="preserve">Baker — prototype bill of materials (India-sourced)</t>
@@ -2201,11 +2189,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="95840242"/>
-        <c:axId val="31076756"/>
+        <c:axId val="28548920"/>
+        <c:axId val="89470169"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="95840242"/>
+        <c:axId val="28548920"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2237,7 +2225,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="31076756"/>
+        <c:crossAx val="89470169"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2245,7 +2233,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="31076756"/>
+        <c:axId val="89470169"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2287,7 +2275,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="95840242"/>
+        <c:crossAx val="28548920"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2515,11 +2503,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="69033556"/>
-        <c:axId val="49193885"/>
+        <c:axId val="73308404"/>
+        <c:axId val="96403699"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="69033556"/>
+        <c:axId val="73308404"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -2551,7 +2539,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="49193885"/>
+        <c:crossAx val="96403699"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2559,7 +2547,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="49193885"/>
+        <c:axId val="96403699"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2591,7 +2579,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="69033556"/>
+        <c:crossAx val="73308404"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2759,11 +2747,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="47919889"/>
-        <c:axId val="23178642"/>
+        <c:axId val="79528690"/>
+        <c:axId val="82277349"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="47919889"/>
+        <c:axId val="79528690"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -2795,7 +2783,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="23178642"/>
+        <c:crossAx val="82277349"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2803,7 +2791,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="23178642"/>
+        <c:axId val="82277349"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2835,7 +2823,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="47919889"/>
+        <c:crossAx val="79528690"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3562,57 +3550,57 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="B6" s="5" t="n">
         <f aca="false">'Mixer Cost Breakup'!E9</f>
         <v>62211.88</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="B7" s="5" t="n">
         <f aca="false">'Mixer Cost Breakup'!G9</f>
         <v>2872.408</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="B8" s="7" t="n">
         <f aca="false">B6+B7</f>
@@ -3622,31 +3610,31 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="B9" s="7" t="n">
         <f aca="false">B8*Inputs!$B$7</f>
         <v>9762.6432</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="26" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="B10" s="27" t="n">
         <f aca="false">B8+B9</f>
         <v>74846.9312</v>
       </c>
       <c r="C10" s="52" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="B11" s="31" t="str">
         <f aca="false">IF(ABS(B10-'Mixer Cost Breakup'!J9)&lt;1,"OK","MISMATCH")</f>
@@ -3655,7 +3643,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="B12" s="15" t="str">
         <f aca="false">COUNTIF('Mixer BOM'!K5:K30,"Listing")&amp;" of "&amp;COUNTA('Mixer BOM'!D5:D30)</f>
@@ -3664,12 +3652,12 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>44</v>
@@ -3680,26 +3668,26 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="16" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="B16" s="7" t="n">
         <f aca="false">B10</f>
         <v>74846.9312</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="53" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="B17" s="54" t="n">
         <f aca="false">'Mixer Production (CN)'!I31</f>
         <v>13740.256</v>
       </c>
       <c r="C17" s="52" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3711,24 +3699,24 @@
         <v>15000</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="16" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B19" s="6" t="n">
         <f aca="false">B18-B17</f>
         <v>1259.744</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="16" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="B20" s="30" t="n">
         <f aca="false">IF(B18=0,0,B17/B18)</f>
@@ -3738,7 +3726,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="16" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="B21" s="7" t="n">
         <f aca="false">B16-B17</f>
@@ -3748,7 +3736,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="16" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="B22" s="30" t="n">
         <f aca="false">IF(B16=0,0,B21/B16)</f>
@@ -3758,26 +3746,26 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="16" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="B23" s="7" t="n">
         <f aca="false">B17*(1+Inputs!$B$16)</f>
         <v>15114.2816</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="16" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="B24" s="6" t="n">
         <f aca="false">B18-B23</f>
         <v>-114.2816</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
     </row>
   </sheetData>
@@ -3808,12 +3796,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3824,198 +3812,198 @@
         <v>28</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B5" s="55" t="n">
         <v>88</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="B6" s="20" t="n">
         <v>0.35</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="B7" s="20" t="n">
         <v>0.15</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="B8" s="20" t="n">
         <v>0.165</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="B9" s="19" t="n">
         <v>3520</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="B10" s="19" t="n">
         <v>176</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="B11" s="19" t="n">
         <v>12000</v>
       </c>
       <c r="C11" s="16" t="s">
+        <v>414</v>
+      </c>
+      <c r="D11" s="18" t="s">
         <v>418</v>
-      </c>
-      <c r="D11" s="18" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="16" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="B12" s="19" t="n">
         <v>2000</v>
       </c>
       <c r="C12" s="16" t="s">
+        <v>414</v>
+      </c>
+      <c r="D12" s="18" t="s">
         <v>418</v>
-      </c>
-      <c r="D12" s="18" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="16" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="B13" s="19" t="n">
         <v>150000</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="16" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="B14" s="19" t="n">
         <v>15000</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="16" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="B15" s="17" t="n">
         <v>100</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="16" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="B16" s="20" t="n">
         <v>0.1</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="31" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="56" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="57" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
     </row>
   </sheetData>
@@ -4035,7 +4023,7 @@
     <tabColor rgb="FFC00000"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="52"/>
@@ -4181,413 +4169,378 @@
       <c r="A16" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="B16" s="5" t="n">
-        <f aca="false">'Mixer Final Cost'!B10</f>
-        <v>74846.9312</v>
+      <c r="B16" s="22" t="n">
+        <v>100000</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E16" s="21" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="16" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B17" s="22" t="n">
-        <v>100000</v>
+        <v>60000</v>
       </c>
       <c r="C17" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="E17" s="21" t="s">
         <v>55</v>
-      </c>
-      <c r="D17" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="E17" s="21" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="B18" s="22" t="n">
-        <v>60000</v>
+      <c r="B18" s="7" t="n">
+        <f aca="false">$B$7*$B$8*$B$6</f>
+        <v>450000</v>
       </c>
       <c r="C18" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="D18" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="E18" s="21" t="s">
         <v>55</v>
-      </c>
-      <c r="D18" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="E18" s="21" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="B19" s="22" t="n">
-        <v>60000</v>
+        <v>61</v>
+      </c>
+      <c r="B19" s="7" t="n">
+        <f aca="false">$B$9*$B$6</f>
+        <v>0</v>
       </c>
       <c r="C19" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="D19" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="E19" s="21" t="s">
         <v>55</v>
-      </c>
-      <c r="D19" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="E19" s="21" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B20" s="7" t="n">
-        <f aca="false">$B$7*$B$8*$B$6</f>
-        <v>450000</v>
+        <f aca="false">$B$10*$B$6</f>
+        <v>135000</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D20" s="18" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E20" s="21" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="B21" s="7" t="n">
-        <f aca="false">$B$9*$B$6</f>
-        <v>0</v>
+        <v>66</v>
+      </c>
+      <c r="B21" s="22" t="n">
+        <v>100000</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E21" s="21" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="B22" s="22" t="n">
+        <v>50000</v>
+      </c>
+      <c r="C22" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="B22" s="7" t="n">
-        <f aca="false">$B$10*$B$6</f>
-        <v>135000</v>
-      </c>
-      <c r="C22" s="16" t="s">
-        <v>68</v>
-      </c>
       <c r="D22" s="18" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E22" s="21" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B23" s="22" t="n">
-        <v>100000</v>
+        <v>75000</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D23" s="18" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E23" s="21" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B24" s="22" t="n">
         <v>50000</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D24" s="18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E24" s="21" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="B25" s="22" t="n">
-        <v>75000</v>
-      </c>
-      <c r="C25" s="16" t="s">
+      <c r="A25" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="D25" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="E25" s="21" t="s">
-        <v>57</v>
-      </c>
+      <c r="B25" s="23" t="n">
+        <f aca="false">SUM(B15:B24)</f>
+        <v>1393417.9444</v>
+      </c>
+      <c r="C25" s="24"/>
+      <c r="D25" s="24"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="B26" s="25" t="n">
+        <f aca="false">SUMIF(E15:E24,"N",B15:B24)</f>
+        <v>1020000</v>
+      </c>
+      <c r="C26" s="24"/>
+      <c r="D26" s="24"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="26" t="s">
         <v>78</v>
       </c>
-      <c r="B26" s="22" t="n">
-        <v>50000</v>
-      </c>
-      <c r="C26" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="D26" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="E26" s="21" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="B27" s="23" t="n">
-        <f aca="false">SUM(B15:B26)</f>
-        <v>1528264.8756</v>
-      </c>
-      <c r="C27" s="24"/>
-      <c r="D27" s="24"/>
+      <c r="B27" s="27" t="n">
+        <f aca="false">ROUND((B25+B26*$B$11)/100000,0)*100000</f>
+        <v>1500000</v>
+      </c>
+      <c r="C27" s="28"/>
+      <c r="D27" s="28"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="B28" s="25" t="n">
+        <f aca="false">B27-B25</f>
+        <v>106582.0556</v>
+      </c>
+      <c r="C28" s="29" t="n">
+        <f aca="false">IF(B26=0,0,B28/B26)</f>
+        <v>0.104492211372549</v>
+      </c>
+      <c r="D28" s="18" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="B28" s="25" t="n">
-        <f aca="false">SUMIF(E15:E26,"N",B15:B26)</f>
-        <v>1080000</v>
-      </c>
-      <c r="C28" s="24"/>
-      <c r="D28" s="24"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="26" t="s">
+    </row>
+    <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B29" s="27" t="n">
-        <f aca="false">ROUND((B27+B28*$B$11)/100000,0)*100000</f>
-        <v>1600000</v>
-      </c>
-      <c r="C29" s="28"/>
-      <c r="D29" s="28"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="B30" s="25" t="n">
-        <f aca="false">B29-B27</f>
-        <v>71735.1244000001</v>
-      </c>
-      <c r="C30" s="29" t="n">
-        <f aca="false">IF(B28=0,0,B30/B28)</f>
-        <v>0.0664214114814816</v>
-      </c>
-      <c r="D30" s="18" t="s">
-        <v>84</v>
-      </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="11" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>86</v>
+      <c r="A32" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="B32" s="7" t="n">
+        <f aca="false">SUMIF($C$15:$C$24,A32,$B$15:$B$24)</f>
+        <v>373417.9444</v>
+      </c>
+      <c r="C32" s="30" t="n">
+        <f aca="false">IF($B$27=0,0,B32/$B$27)</f>
+        <v>0.248945296266667</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="B33" s="7" t="n">
+        <f aca="false">SUMIF($C$15:$C$24,A33,$B$15:$B$24)</f>
+        <v>160000</v>
+      </c>
+      <c r="C33" s="30" t="n">
+        <f aca="false">IF($B$27=0,0,B33/$B$27)</f>
+        <v>0.106666666666667</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="16" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="B34" s="7" t="n">
-        <f aca="false">SUMIF($C$15:$C$26,A34,$B$15:$B$26)</f>
-        <v>448264.8756</v>
+        <f aca="false">SUMIF($C$15:$C$24,A34,$B$15:$B$24)</f>
+        <v>450000</v>
       </c>
       <c r="C34" s="30" t="n">
-        <f aca="false">IF($B$29=0,0,B34/$B$29)</f>
-        <v>0.28016554725</v>
+        <f aca="false">IF($B$27=0,0,B34/$B$27)</f>
+        <v>0.3</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="16" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="B35" s="7" t="n">
-        <f aca="false">SUMIF($C$15:$C$26,A35,$B$15:$B$26)</f>
-        <v>220000</v>
+        <f aca="false">SUMIF($C$15:$C$24,A35,$B$15:$B$24)</f>
+        <v>135000</v>
       </c>
       <c r="C35" s="30" t="n">
-        <f aca="false">IF($B$29=0,0,B35/$B$29)</f>
-        <v>0.1375</v>
+        <f aca="false">IF($B$27=0,0,B35/$B$27)</f>
+        <v>0.09</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="16" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B36" s="7" t="n">
-        <f aca="false">SUMIF($C$15:$C$26,A36,$B$15:$B$26)</f>
-        <v>450000</v>
+        <f aca="false">SUMIF($C$15:$C$24,A36,$B$15:$B$24)</f>
+        <v>150000</v>
       </c>
       <c r="C36" s="30" t="n">
-        <f aca="false">IF($B$29=0,0,B36/$B$29)</f>
-        <v>0.28125</v>
+        <f aca="false">IF($B$27=0,0,B36/$B$27)</f>
+        <v>0.1</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="16" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B37" s="7" t="n">
-        <f aca="false">SUMIF($C$15:$C$26,A37,$B$15:$B$26)</f>
-        <v>135000</v>
+        <f aca="false">SUMIF($C$15:$C$24,A37,$B$15:$B$24)+B28</f>
+        <v>231582.0556</v>
       </c>
       <c r="C37" s="30" t="n">
-        <f aca="false">IF($B$29=0,0,B37/$B$29)</f>
-        <v>0.084375</v>
+        <f aca="false">IF($B$27=0,0,B37/$B$27)</f>
+        <v>0.154388037066667</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="B38" s="7" t="n">
-        <f aca="false">SUMIF($C$15:$C$26,A38,$B$15:$B$26)</f>
-        <v>150000</v>
-      </c>
-      <c r="C38" s="30" t="n">
-        <f aca="false">IF($B$29=0,0,B38/$B$29)</f>
-        <v>0.09375</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="B39" s="7" t="n">
-        <f aca="false">SUMIF($C$15:$C$26,A39,$B$15:$B$26)+B30</f>
-        <v>196735.1244</v>
-      </c>
-      <c r="C39" s="30" t="n">
-        <f aca="false">IF($B$29=0,0,B39/$B$29)</f>
-        <v>0.12295945275</v>
+      <c r="A38" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B38" s="31" t="str">
+        <f aca="false">IF(ABS(SUM(B32:B37)-B27)&lt;1,"OK","MISMATCH")</f>
+        <v>OK</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="2" t="s">
+      <c r="A40" s="11" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="B40" s="31" t="str">
-        <f aca="false">IF(ABS(SUM(B34:B39)-B29)&lt;1,"OK","MISMATCH")</f>
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="11" t="s">
+      <c r="D41" s="3" t="s">
         <v>88</v>
       </c>
     </row>
+    <row r="42" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="B42" s="22" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="C42" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="D42" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
     <row r="43" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D43" s="3" t="s">
+      <c r="A43" s="33" t="s">
         <v>92</v>
+      </c>
+      <c r="B43" s="34" t="n">
+        <f aca="false">B27</f>
+        <v>1500000</v>
+      </c>
+      <c r="C43" s="28" t="str">
+        <f aca="false">B6&amp;" months"</f>
+        <v>9 months</v>
+      </c>
+      <c r="D43" s="35" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="B44" s="22" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="C44" s="24" t="s">
         <v>94</v>
+      </c>
+      <c r="B44" s="7" t="n">
+        <f aca="false">ROUND((B27+'Mixer Final Cost'!B10+60000+'Baker Final Cost'!B10+$B$8*$B$6+250000)/100000,0)*100000</f>
+        <v>2700000</v>
+      </c>
+      <c r="C44" s="24" t="str">
+        <f aca="false">B6&amp;" months"</f>
+        <v>9 months</v>
       </c>
       <c r="D44" s="32" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="33" t="s">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="2" t="s">
         <v>96</v>
-      </c>
-      <c r="B45" s="34" t="n">
-        <f aca="false">B29</f>
-        <v>1600000</v>
-      </c>
-      <c r="C45" s="28" t="str">
-        <f aca="false">B6&amp;" months"</f>
-        <v>9 months</v>
-      </c>
-      <c r="D45" s="35" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="B46" s="7" t="n">
-        <f aca="false">ROUND((B29+'Baker Final Cost'!B10+$B$8*$B$6+250000)/100000,0)*100000</f>
-        <v>2700000</v>
-      </c>
-      <c r="C46" s="24" t="str">
-        <f aca="false">B6&amp;" months"</f>
-        <v>9 months</v>
-      </c>
-      <c r="D46" s="32" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="2" t="s">
-        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -4626,50 +4579,50 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="K4" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="L4" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4677,13 +4630,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C5" s="36" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D5" s="37" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E5" s="38" t="n">
         <v>8</v>
@@ -4692,7 +4645,7 @@
         <v>949</v>
       </c>
       <c r="G5" s="38" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H5" s="40" t="n">
         <f aca="false">IF(G5="USD",F5*Inputs!$B$5,F5)</f>
@@ -4707,10 +4660,10 @@
         <v>No</v>
       </c>
       <c r="K5" s="36" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L5" s="36" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4718,13 +4671,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D6" s="42" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E6" s="43" t="n">
         <v>1</v>
@@ -4733,7 +4686,7 @@
         <v>2500</v>
       </c>
       <c r="G6" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H6" s="5" t="n">
         <f aca="false">IF(G6="USD",F6*Inputs!$B$5,F6)</f>
@@ -4748,7 +4701,7 @@
         <v>No</v>
       </c>
       <c r="K6" s="16" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="L6" s="16"/>
     </row>
@@ -4757,13 +4710,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D7" s="42" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E7" s="43" t="n">
         <v>3</v>
@@ -4772,7 +4725,7 @@
         <v>375</v>
       </c>
       <c r="G7" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H7" s="5" t="n">
         <f aca="false">IF(G7="USD",F7*Inputs!$B$5,F7)</f>
@@ -4787,10 +4740,10 @@
         <v>No</v>
       </c>
       <c r="K7" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L7" s="16" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4798,13 +4751,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D8" s="42" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E8" s="43" t="n">
         <v>4</v>
@@ -4813,7 +4766,7 @@
         <v>900</v>
       </c>
       <c r="G8" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H8" s="5" t="n">
         <f aca="false">IF(G8="USD",F8*Inputs!$B$5,F8)</f>
@@ -4828,10 +4781,10 @@
         <v>No</v>
       </c>
       <c r="K8" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="L8" s="16" t="s">
         <v>122</v>
-      </c>
-      <c r="L8" s="16" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4839,13 +4792,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D9" s="42" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E9" s="43" t="n">
         <v>1</v>
@@ -4854,7 +4807,7 @@
         <v>2500</v>
       </c>
       <c r="G9" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H9" s="5" t="n">
         <f aca="false">IF(G9="USD",F9*Inputs!$B$5,F9)</f>
@@ -4869,10 +4822,10 @@
         <v>No</v>
       </c>
       <c r="K9" s="16" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="L9" s="16" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4880,13 +4833,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D10" s="42" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E10" s="43" t="n">
         <v>2</v>
@@ -4895,7 +4848,7 @@
         <v>44</v>
       </c>
       <c r="G10" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H10" s="5" t="n">
         <f aca="false">IF(G10="USD",F10*Inputs!$B$5,F10)</f>
@@ -4910,10 +4863,10 @@
         <v>No</v>
       </c>
       <c r="K10" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L10" s="16" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4921,13 +4874,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D11" s="42" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E11" s="43" t="n">
         <v>1</v>
@@ -4936,7 +4889,7 @@
         <v>200</v>
       </c>
       <c r="G11" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H11" s="5" t="n">
         <f aca="false">IF(G11="USD",F11*Inputs!$B$5,F11)</f>
@@ -4951,10 +4904,10 @@
         <v>No</v>
       </c>
       <c r="K11" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L11" s="16" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4962,13 +4915,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D12" s="42" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E12" s="43" t="n">
         <v>2</v>
@@ -4977,7 +4930,7 @@
         <v>29.49</v>
       </c>
       <c r="G12" s="43" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H12" s="5" t="n">
         <f aca="false">IF(G12="USD",F12*Inputs!$B$5,F12)</f>
@@ -4992,10 +4945,10 @@
         <v>Yes</v>
       </c>
       <c r="K12" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L12" s="16" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5003,13 +4956,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C13" s="36" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D13" s="37" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E13" s="38" t="n">
         <v>3</v>
@@ -5018,7 +4971,7 @@
         <v>15000</v>
       </c>
       <c r="G13" s="38" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H13" s="40" t="n">
         <f aca="false">IF(G13="USD",F13*Inputs!$B$5,F13)</f>
@@ -5033,10 +4986,10 @@
         <v>No</v>
       </c>
       <c r="K13" s="36" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L13" s="36" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5044,13 +4997,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D14" s="42" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E14" s="43" t="n">
         <v>3</v>
@@ -5059,7 +5012,7 @@
         <v>1529</v>
       </c>
       <c r="G14" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H14" s="5" t="n">
         <f aca="false">IF(G14="USD",F14*Inputs!$B$5,F14)</f>
@@ -5074,10 +5027,10 @@
         <v>No</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L14" s="16" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5085,13 +5038,13 @@
         <v>11</v>
       </c>
       <c r="B15" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="D15" s="42" t="s">
         <v>134</v>
-      </c>
-      <c r="C15" s="16" t="s">
-        <v>135</v>
-      </c>
-      <c r="D15" s="42" t="s">
-        <v>138</v>
       </c>
       <c r="E15" s="43" t="n">
         <v>2</v>
@@ -5100,7 +5053,7 @@
         <v>84.99</v>
       </c>
       <c r="G15" s="43" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H15" s="5" t="n">
         <f aca="false">IF(G15="USD",F15*Inputs!$B$5,F15)</f>
@@ -5115,10 +5068,10 @@
         <v>Yes</v>
       </c>
       <c r="K15" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L15" s="16" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5126,13 +5079,13 @@
         <v>12</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D16" s="42" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E16" s="43" t="n">
         <v>3</v>
@@ -5141,7 +5094,7 @@
         <v>847</v>
       </c>
       <c r="G16" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H16" s="5" t="n">
         <f aca="false">IF(G16="USD",F16*Inputs!$B$5,F16)</f>
@@ -5156,10 +5109,10 @@
         <v>No</v>
       </c>
       <c r="K16" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L16" s="16" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5167,13 +5120,13 @@
         <v>13</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D17" s="42" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="E17" s="43" t="n">
         <v>6</v>
@@ -5182,7 +5135,7 @@
         <v>980</v>
       </c>
       <c r="G17" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H17" s="5" t="n">
         <f aca="false">IF(G17="USD",F17*Inputs!$B$5,F17)</f>
@@ -5197,10 +5150,10 @@
         <v>No</v>
       </c>
       <c r="K17" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L17" s="16" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5208,13 +5161,13 @@
         <v>14</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D18" s="42" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E18" s="43" t="n">
         <v>8</v>
@@ -5223,7 +5176,7 @@
         <v>619</v>
       </c>
       <c r="G18" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H18" s="5" t="n">
         <f aca="false">IF(G18="USD",F18*Inputs!$B$5,F18)</f>
@@ -5238,10 +5191,10 @@
         <v>No</v>
       </c>
       <c r="K18" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L18" s="16" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5249,13 +5202,13 @@
         <v>15</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D19" s="42" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="E19" s="43" t="n">
         <v>10</v>
@@ -5264,7 +5217,7 @@
         <v>41</v>
       </c>
       <c r="G19" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H19" s="5" t="n">
         <f aca="false">IF(G19="USD",F19*Inputs!$B$5,F19)</f>
@@ -5279,10 +5232,10 @@
         <v>No</v>
       </c>
       <c r="K19" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L19" s="16" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5290,13 +5243,13 @@
         <v>16</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D20" s="42" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="E20" s="43" t="n">
         <v>3</v>
@@ -5305,7 +5258,7 @@
         <v>264</v>
       </c>
       <c r="G20" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H20" s="5" t="n">
         <f aca="false">IF(G20="USD",F20*Inputs!$B$5,F20)</f>
@@ -5320,10 +5273,10 @@
         <v>No</v>
       </c>
       <c r="K20" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L20" s="16" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5331,13 +5284,13 @@
         <v>17</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D21" s="42" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="E21" s="43" t="n">
         <v>4</v>
@@ -5346,7 +5299,7 @@
         <v>269</v>
       </c>
       <c r="G21" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H21" s="5" t="n">
         <f aca="false">IF(G21="USD",F21*Inputs!$B$5,F21)</f>
@@ -5361,10 +5314,10 @@
         <v>No</v>
       </c>
       <c r="K21" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L21" s="16" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5372,13 +5325,13 @@
         <v>18</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D22" s="42" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="E22" s="43" t="n">
         <v>3</v>
@@ -5387,7 +5340,7 @@
         <v>62</v>
       </c>
       <c r="G22" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H22" s="5" t="n">
         <f aca="false">IF(G22="USD",F22*Inputs!$B$5,F22)</f>
@@ -5402,10 +5355,10 @@
         <v>No</v>
       </c>
       <c r="K22" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L22" s="16" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5413,13 +5366,13 @@
         <v>19</v>
       </c>
       <c r="B23" s="36" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C23" s="36" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D23" s="37" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E23" s="38" t="n">
         <v>1</v>
@@ -5428,7 +5381,7 @@
         <v>85.99</v>
       </c>
       <c r="G23" s="38" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H23" s="40" t="n">
         <f aca="false">IF(G23="USD",F23*Inputs!$B$5,F23)</f>
@@ -5443,10 +5396,10 @@
         <v>Yes</v>
       </c>
       <c r="K23" s="36" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L23" s="36" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5454,13 +5407,13 @@
         <v>20</v>
       </c>
       <c r="B24" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="D24" s="42" t="s">
         <v>149</v>
-      </c>
-      <c r="C24" s="16" t="s">
-        <v>150</v>
-      </c>
-      <c r="D24" s="42" t="s">
-        <v>153</v>
       </c>
       <c r="E24" s="43" t="n">
         <v>1</v>
@@ -5469,7 +5422,7 @@
         <v>3721</v>
       </c>
       <c r="G24" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H24" s="5" t="n">
         <f aca="false">IF(G24="USD",F24*Inputs!$B$5,F24)</f>
@@ -5484,10 +5437,10 @@
         <v>No</v>
       </c>
       <c r="K24" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L24" s="16" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5495,13 +5448,13 @@
         <v>21</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D25" s="42" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="E25" s="43" t="n">
         <v>1</v>
@@ -5510,7 +5463,7 @@
         <v>14396</v>
       </c>
       <c r="G25" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H25" s="5" t="n">
         <f aca="false">IF(G25="USD",F25*Inputs!$B$5,F25)</f>
@@ -5525,10 +5478,10 @@
         <v>No</v>
       </c>
       <c r="K25" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L25" s="16" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5536,13 +5489,13 @@
         <v>22</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D26" s="42" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E26" s="43" t="n">
         <v>1</v>
@@ -5551,7 +5504,7 @@
         <v>4889</v>
       </c>
       <c r="G26" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H26" s="5" t="n">
         <f aca="false">IF(G26="USD",F26*Inputs!$B$5,F26)</f>
@@ -5566,10 +5519,10 @@
         <v>No</v>
       </c>
       <c r="K26" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L26" s="16" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5577,13 +5530,13 @@
         <v>23</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D27" s="42" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="E27" s="43" t="n">
         <v>1</v>
@@ -5592,7 +5545,7 @@
         <v>23.99</v>
       </c>
       <c r="G27" s="43" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H27" s="5" t="n">
         <f aca="false">IF(G27="USD",F27*Inputs!$B$5,F27)</f>
@@ -5607,10 +5560,10 @@
         <v>Yes</v>
       </c>
       <c r="K27" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L27" s="16" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5618,13 +5571,13 @@
         <v>24</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D28" s="42" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="E28" s="43" t="n">
         <v>1</v>
@@ -5633,7 +5586,7 @@
         <v>1500</v>
       </c>
       <c r="G28" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H28" s="5" t="n">
         <f aca="false">IF(G28="USD",F28*Inputs!$B$5,F28)</f>
@@ -5648,10 +5601,10 @@
         <v>No</v>
       </c>
       <c r="K28" s="16" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="L28" s="16" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5659,13 +5612,13 @@
         <v>25</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D29" s="42" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E29" s="43" t="n">
         <v>1</v>
@@ -5674,7 +5627,7 @@
         <v>3786</v>
       </c>
       <c r="G29" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H29" s="5" t="n">
         <f aca="false">IF(G29="USD",F29*Inputs!$B$5,F29)</f>
@@ -5689,10 +5642,10 @@
         <v>No</v>
       </c>
       <c r="K29" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L29" s="16" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5700,13 +5653,13 @@
         <v>26</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D30" s="42" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="E30" s="43" t="n">
         <v>1</v>
@@ -5715,7 +5668,7 @@
         <v>300</v>
       </c>
       <c r="G30" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H30" s="5" t="n">
         <f aca="false">IF(G30="USD",F30*Inputs!$B$5,F30)</f>
@@ -5730,7 +5683,7 @@
         <v>No</v>
       </c>
       <c r="K30" s="16" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="L30" s="16"/>
     </row>
@@ -5739,13 +5692,13 @@
         <v>27</v>
       </c>
       <c r="B31" s="36" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C31" s="36" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D31" s="37" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="E31" s="38" t="n">
         <v>10</v>
@@ -5754,7 +5707,7 @@
         <v>50</v>
       </c>
       <c r="G31" s="38" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H31" s="40" t="n">
         <f aca="false">IF(G31="USD",F31*Inputs!$B$5,F31)</f>
@@ -5769,10 +5722,10 @@
         <v>No</v>
       </c>
       <c r="K31" s="36" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L31" s="36" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5780,13 +5733,13 @@
         <v>28</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D32" s="42" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="E32" s="43" t="n">
         <v>20</v>
@@ -5795,7 +5748,7 @@
         <v>11.5</v>
       </c>
       <c r="G32" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H32" s="5" t="n">
         <f aca="false">IF(G32="USD",F32*Inputs!$B$5,F32)</f>
@@ -5810,10 +5763,10 @@
         <v>No</v>
       </c>
       <c r="K32" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L32" s="16" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5821,13 +5774,13 @@
         <v>29</v>
       </c>
       <c r="B33" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="C33" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="D33" s="42" t="s">
         <v>163</v>
-      </c>
-      <c r="C33" s="16" t="s">
-        <v>164</v>
-      </c>
-      <c r="D33" s="42" t="s">
-        <v>167</v>
       </c>
       <c r="E33" s="43" t="n">
         <v>1</v>
@@ -5836,7 +5789,7 @@
         <v>14999</v>
       </c>
       <c r="G33" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H33" s="5" t="n">
         <f aca="false">IF(G33="USD",F33*Inputs!$B$5,F33)</f>
@@ -5851,10 +5804,10 @@
         <v>No</v>
       </c>
       <c r="K33" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L33" s="16" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5862,13 +5815,13 @@
         <v>30</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D34" s="42" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E34" s="43" t="n">
         <v>1</v>
@@ -5877,7 +5830,7 @@
         <v>56.68</v>
       </c>
       <c r="G34" s="43" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H34" s="5" t="n">
         <f aca="false">IF(G34="USD",F34*Inputs!$B$5,F34)</f>
@@ -5892,10 +5845,10 @@
         <v>Yes</v>
       </c>
       <c r="K34" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L34" s="16" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5903,13 +5856,13 @@
         <v>31</v>
       </c>
       <c r="B35" s="16" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C35" s="16" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D35" s="42" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="E35" s="43" t="n">
         <v>1</v>
@@ -5918,7 +5871,7 @@
         <v>8000</v>
       </c>
       <c r="G35" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H35" s="5" t="n">
         <f aca="false">IF(G35="USD",F35*Inputs!$B$5,F35)</f>
@@ -5933,10 +5886,10 @@
         <v>No</v>
       </c>
       <c r="K35" s="16" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="L35" s="16" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5944,13 +5897,13 @@
         <v>32</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D36" s="42" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="E36" s="43" t="n">
         <v>1</v>
@@ -5959,7 +5912,7 @@
         <v>659</v>
       </c>
       <c r="G36" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H36" s="5" t="n">
         <f aca="false">IF(G36="USD",F36*Inputs!$B$5,F36)</f>
@@ -5974,10 +5927,10 @@
         <v>No</v>
       </c>
       <c r="K36" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L36" s="16" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5985,13 +5938,13 @@
         <v>33</v>
       </c>
       <c r="B37" s="16" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D37" s="42" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="E37" s="43" t="n">
         <v>2</v>
@@ -6000,7 +5953,7 @@
         <v>1500</v>
       </c>
       <c r="G37" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H37" s="5" t="n">
         <f aca="false">IF(G37="USD",F37*Inputs!$B$5,F37)</f>
@@ -6015,10 +5968,10 @@
         <v>No</v>
       </c>
       <c r="K37" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L37" s="16" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6026,13 +5979,13 @@
         <v>34</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D38" s="42" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="E38" s="43" t="n">
         <v>2</v>
@@ -6041,7 +5994,7 @@
         <v>91</v>
       </c>
       <c r="G38" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H38" s="5" t="n">
         <f aca="false">IF(G38="USD",F38*Inputs!$B$5,F38)</f>
@@ -6056,10 +6009,10 @@
         <v>No</v>
       </c>
       <c r="K38" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L38" s="16" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6067,13 +6020,13 @@
         <v>35</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C39" s="16" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D39" s="42" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E39" s="43" t="n">
         <v>1</v>
@@ -6082,7 +6035,7 @@
         <v>500</v>
       </c>
       <c r="G39" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H39" s="5" t="n">
         <f aca="false">IF(G39="USD",F39*Inputs!$B$5,F39)</f>
@@ -6097,7 +6050,7 @@
         <v>No</v>
       </c>
       <c r="K39" s="16" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="L39" s="16"/>
     </row>
@@ -6106,13 +6059,13 @@
         <v>36</v>
       </c>
       <c r="B40" s="36" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C40" s="36" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D40" s="37" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="E40" s="38" t="n">
         <v>1</v>
@@ -6121,7 +6074,7 @@
         <v>3150</v>
       </c>
       <c r="G40" s="38" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H40" s="40" t="n">
         <f aca="false">IF(G40="USD",F40*Inputs!$B$5,F40)</f>
@@ -6136,10 +6089,10 @@
         <v>No</v>
       </c>
       <c r="K40" s="36" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L40" s="36" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6147,13 +6100,13 @@
         <v>37</v>
       </c>
       <c r="B41" s="16" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C41" s="16" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D41" s="42" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="E41" s="43" t="n">
         <v>4</v>
@@ -6162,7 +6115,7 @@
         <v>259</v>
       </c>
       <c r="G41" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H41" s="5" t="n">
         <f aca="false">IF(G41="USD",F41*Inputs!$B$5,F41)</f>
@@ -6177,10 +6130,10 @@
         <v>No</v>
       </c>
       <c r="K41" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L41" s="16" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6188,13 +6141,13 @@
         <v>38</v>
       </c>
       <c r="B42" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="C42" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="D42" s="42" t="s">
         <v>177</v>
-      </c>
-      <c r="C42" s="16" t="s">
-        <v>178</v>
-      </c>
-      <c r="D42" s="42" t="s">
-        <v>181</v>
       </c>
       <c r="E42" s="43" t="n">
         <v>1</v>
@@ -6203,7 +6156,7 @@
         <v>300</v>
       </c>
       <c r="G42" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H42" s="5" t="n">
         <f aca="false">IF(G42="USD",F42*Inputs!$B$5,F42)</f>
@@ -6218,10 +6171,10 @@
         <v>No</v>
       </c>
       <c r="K42" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L42" s="16" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6229,13 +6182,13 @@
         <v>39</v>
       </c>
       <c r="B43" s="16" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C43" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="D43" s="42" t="s">
         <v>178</v>
-      </c>
-      <c r="D43" s="42" t="s">
-        <v>182</v>
       </c>
       <c r="E43" s="43" t="n">
         <v>1</v>
@@ -6244,7 +6197,7 @@
         <v>819</v>
       </c>
       <c r="G43" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H43" s="5" t="n">
         <f aca="false">IF(G43="USD",F43*Inputs!$B$5,F43)</f>
@@ -6259,10 +6212,10 @@
         <v>No</v>
       </c>
       <c r="K43" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L43" s="16" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6270,13 +6223,13 @@
         <v>40</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D44" s="42" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="E44" s="43" t="n">
         <v>1</v>
@@ -6285,7 +6238,7 @@
         <v>500</v>
       </c>
       <c r="G44" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H44" s="5" t="n">
         <f aca="false">IF(G44="USD",F44*Inputs!$B$5,F44)</f>
@@ -6300,7 +6253,7 @@
         <v>No</v>
       </c>
       <c r="K44" s="16" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="L44" s="16"/>
     </row>
@@ -6309,13 +6262,13 @@
         <v>41</v>
       </c>
       <c r="B45" s="36" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C45" s="36" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D45" s="37" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="E45" s="38" t="n">
         <v>1</v>
@@ -6324,7 +6277,7 @@
         <v>1500</v>
       </c>
       <c r="G45" s="38" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H45" s="40" t="n">
         <f aca="false">IF(G45="USD",F45*Inputs!$B$5,F45)</f>
@@ -6339,10 +6292,10 @@
         <v>No</v>
       </c>
       <c r="K45" s="36" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L45" s="36" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6350,13 +6303,13 @@
         <v>42</v>
       </c>
       <c r="B46" s="16" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C46" s="16" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D46" s="42" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="E46" s="43" t="n">
         <v>1</v>
@@ -6365,7 +6318,7 @@
         <v>748</v>
       </c>
       <c r="G46" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H46" s="5" t="n">
         <f aca="false">IF(G46="USD",F46*Inputs!$B$5,F46)</f>
@@ -6380,10 +6333,10 @@
         <v>No</v>
       </c>
       <c r="K46" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L46" s="16" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6391,13 +6344,13 @@
         <v>43</v>
       </c>
       <c r="B47" s="16" t="s">
+        <v>180</v>
+      </c>
+      <c r="C47" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="D47" s="42" t="s">
         <v>184</v>
-      </c>
-      <c r="C47" s="16" t="s">
-        <v>185</v>
-      </c>
-      <c r="D47" s="42" t="s">
-        <v>188</v>
       </c>
       <c r="E47" s="43" t="n">
         <v>1</v>
@@ -6406,7 +6359,7 @@
         <v>349</v>
       </c>
       <c r="G47" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H47" s="5" t="n">
         <f aca="false">IF(G47="USD",F47*Inputs!$B$5,F47)</f>
@@ -6421,10 +6374,10 @@
         <v>No</v>
       </c>
       <c r="K47" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L47" s="16" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6432,13 +6385,13 @@
         <v>44</v>
       </c>
       <c r="B48" s="16" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C48" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="D48" s="42" t="s">
         <v>185</v>
-      </c>
-      <c r="D48" s="42" t="s">
-        <v>189</v>
       </c>
       <c r="E48" s="43" t="n">
         <v>1</v>
@@ -6447,7 +6400,7 @@
         <v>249</v>
       </c>
       <c r="G48" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H48" s="5" t="n">
         <f aca="false">IF(G48="USD",F48*Inputs!$B$5,F48)</f>
@@ -6462,10 +6415,10 @@
         <v>No</v>
       </c>
       <c r="K48" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L48" s="16" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6473,13 +6426,13 @@
         <v>45</v>
       </c>
       <c r="B49" s="16" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C49" s="16" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D49" s="42" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E49" s="43" t="n">
         <v>1</v>
@@ -6488,7 +6441,7 @@
         <v>850</v>
       </c>
       <c r="G49" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H49" s="5" t="n">
         <f aca="false">IF(G49="USD",F49*Inputs!$B$5,F49)</f>
@@ -6503,10 +6456,10 @@
         <v>No</v>
       </c>
       <c r="K49" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L49" s="16" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6514,13 +6467,13 @@
         <v>46</v>
       </c>
       <c r="B50" s="16" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C50" s="16" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D50" s="42" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="E50" s="43" t="n">
         <v>1</v>
@@ -6529,7 +6482,7 @@
         <v>268</v>
       </c>
       <c r="G50" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H50" s="5" t="n">
         <f aca="false">IF(G50="USD",F50*Inputs!$B$5,F50)</f>
@@ -6544,10 +6497,10 @@
         <v>No</v>
       </c>
       <c r="K50" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L50" s="16" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6555,13 +6508,13 @@
         <v>47</v>
       </c>
       <c r="B51" s="16" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C51" s="16" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D51" s="42" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E51" s="43" t="n">
         <v>1</v>
@@ -6570,7 +6523,7 @@
         <v>569</v>
       </c>
       <c r="G51" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H51" s="5" t="n">
         <f aca="false">IF(G51="USD",F51*Inputs!$B$5,F51)</f>
@@ -6585,10 +6538,10 @@
         <v>No</v>
       </c>
       <c r="K51" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L51" s="16" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6596,13 +6549,13 @@
         <v>48</v>
       </c>
       <c r="B52" s="16" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C52" s="16" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D52" s="42" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="E52" s="43" t="n">
         <v>1</v>
@@ -6611,7 +6564,7 @@
         <v>2</v>
       </c>
       <c r="G52" s="43" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H52" s="5" t="n">
         <f aca="false">IF(G52="USD",F52*Inputs!$B$5,F52)</f>
@@ -6626,10 +6579,10 @@
         <v>Yes</v>
       </c>
       <c r="K52" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L52" s="16" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6637,13 +6590,13 @@
         <v>49</v>
       </c>
       <c r="B53" s="16" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C53" s="16" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D53" s="42" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="E53" s="43" t="n">
         <v>2</v>
@@ -6652,7 +6605,7 @@
         <v>91</v>
       </c>
       <c r="G53" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H53" s="5" t="n">
         <f aca="false">IF(G53="USD",F53*Inputs!$B$5,F53)</f>
@@ -6667,10 +6620,10 @@
         <v>No</v>
       </c>
       <c r="K53" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L53" s="16" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6678,13 +6631,13 @@
         <v>50</v>
       </c>
       <c r="B54" s="36" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C54" s="36" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="D54" s="37" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="E54" s="38" t="n">
         <v>1</v>
@@ -6693,7 +6646,7 @@
         <v>300</v>
       </c>
       <c r="G54" s="38" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H54" s="40" t="n">
         <f aca="false">IF(G54="USD",F54*Inputs!$B$5,F54)</f>
@@ -6708,7 +6661,7 @@
         <v>No</v>
       </c>
       <c r="K54" s="36" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="L54" s="36"/>
     </row>
@@ -6717,13 +6670,13 @@
         <v>51</v>
       </c>
       <c r="B55" s="36" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C55" s="36" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="D55" s="37" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="E55" s="38" t="n">
         <v>1</v>
@@ -6732,7 +6685,7 @@
         <v>13409</v>
       </c>
       <c r="G55" s="38" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H55" s="40" t="n">
         <f aca="false">IF(G55="USD",F55*Inputs!$B$5,F55)</f>
@@ -6747,10 +6700,10 @@
         <v>No</v>
       </c>
       <c r="K55" s="36" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L55" s="36" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6758,13 +6711,13 @@
         <v>52</v>
       </c>
       <c r="B56" s="16" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C56" s="16" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="D56" s="42" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E56" s="43" t="n">
         <v>1</v>
@@ -6773,7 +6726,7 @@
         <v>1204</v>
       </c>
       <c r="G56" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H56" s="5" t="n">
         <f aca="false">IF(G56="USD",F56*Inputs!$B$5,F56)</f>
@@ -6788,10 +6741,10 @@
         <v>No</v>
       </c>
       <c r="K56" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L56" s="16" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6799,13 +6752,13 @@
         <v>53</v>
       </c>
       <c r="B57" s="16" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C57" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="D57" s="42" t="s">
         <v>200</v>
-      </c>
-      <c r="D57" s="42" t="s">
-        <v>204</v>
       </c>
       <c r="E57" s="43" t="n">
         <v>1</v>
@@ -6814,7 +6767,7 @@
         <v>518</v>
       </c>
       <c r="G57" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H57" s="5" t="n">
         <f aca="false">IF(G57="USD",F57*Inputs!$B$5,F57)</f>
@@ -6829,10 +6782,10 @@
         <v>No</v>
       </c>
       <c r="K57" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L57" s="16" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6840,13 +6793,13 @@
         <v>54</v>
       </c>
       <c r="B58" s="16" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C58" s="16" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="D58" s="42" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="E58" s="43" t="n">
         <v>1</v>
@@ -6855,7 +6808,7 @@
         <v>1949</v>
       </c>
       <c r="G58" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H58" s="5" t="n">
         <f aca="false">IF(G58="USD",F58*Inputs!$B$5,F58)</f>
@@ -6870,10 +6823,10 @@
         <v>No</v>
       </c>
       <c r="K58" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L58" s="16" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6881,13 +6834,13 @@
         <v>55</v>
       </c>
       <c r="B59" s="16" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C59" s="16" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="D59" s="42" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E59" s="43" t="n">
         <v>1</v>
@@ -6896,7 +6849,7 @@
         <v>6799</v>
       </c>
       <c r="G59" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H59" s="5" t="n">
         <f aca="false">IF(G59="USD",F59*Inputs!$B$5,F59)</f>
@@ -6911,10 +6864,10 @@
         <v>No</v>
       </c>
       <c r="K59" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L59" s="16" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6922,13 +6875,13 @@
         <v>56</v>
       </c>
       <c r="B60" s="16" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C60" s="16" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="D60" s="42" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="E60" s="43" t="n">
         <v>1</v>
@@ -6937,7 +6890,7 @@
         <v>7619</v>
       </c>
       <c r="G60" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H60" s="5" t="n">
         <f aca="false">IF(G60="USD",F60*Inputs!$B$5,F60)</f>
@@ -6952,10 +6905,10 @@
         <v>No</v>
       </c>
       <c r="K60" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L60" s="16" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6963,13 +6916,13 @@
         <v>57</v>
       </c>
       <c r="B61" s="16" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C61" s="16" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="D61" s="42" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="E61" s="43" t="n">
         <v>1</v>
@@ -6978,7 +6931,7 @@
         <v>2799</v>
       </c>
       <c r="G61" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H61" s="5" t="n">
         <f aca="false">IF(G61="USD",F61*Inputs!$B$5,F61)</f>
@@ -6993,10 +6946,10 @@
         <v>No</v>
       </c>
       <c r="K61" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L61" s="16" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7004,13 +6957,13 @@
         <v>58</v>
       </c>
       <c r="B62" s="16" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C62" s="16" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="D62" s="42" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E62" s="43" t="n">
         <v>1</v>
@@ -7019,7 +6972,7 @@
         <v>3259</v>
       </c>
       <c r="G62" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H62" s="5" t="n">
         <f aca="false">IF(G62="USD",F62*Inputs!$B$5,F62)</f>
@@ -7034,10 +6987,10 @@
         <v>No</v>
       </c>
       <c r="K62" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L62" s="16" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7045,13 +6998,13 @@
         <v>59</v>
       </c>
       <c r="B63" s="16" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C63" s="16" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="D63" s="42" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="E63" s="43" t="n">
         <v>1</v>
@@ -7060,7 +7013,7 @@
         <v>1429</v>
       </c>
       <c r="G63" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H63" s="5" t="n">
         <f aca="false">IF(G63="USD",F63*Inputs!$B$5,F63)</f>
@@ -7075,10 +7028,10 @@
         <v>No</v>
       </c>
       <c r="K63" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L63" s="16" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7086,13 +7039,13 @@
         <v>60</v>
       </c>
       <c r="B64" s="16" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C64" s="16" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="D64" s="42" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E64" s="43" t="n">
         <v>1</v>
@@ -7101,7 +7054,7 @@
         <v>4000</v>
       </c>
       <c r="G64" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H64" s="5" t="n">
         <f aca="false">IF(G64="USD",F64*Inputs!$B$5,F64)</f>
@@ -7116,7 +7069,7 @@
         <v>No</v>
       </c>
       <c r="K64" s="16" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="L64" s="16"/>
     </row>
@@ -7125,13 +7078,13 @@
         <v>61</v>
       </c>
       <c r="B65" s="36" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C65" s="36" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="D65" s="37" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="E65" s="38" t="n">
         <v>1</v>
@@ -7140,7 +7093,7 @@
         <v>43000</v>
       </c>
       <c r="G65" s="38" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H65" s="40" t="n">
         <f aca="false">IF(G65="USD",F65*Inputs!$B$5,F65)</f>
@@ -7155,10 +7108,10 @@
         <v>No</v>
       </c>
       <c r="K65" s="36" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L65" s="36" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7166,13 +7119,13 @@
         <v>62</v>
       </c>
       <c r="B66" s="16" t="s">
+        <v>208</v>
+      </c>
+      <c r="C66" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="D66" s="42" t="s">
         <v>212</v>
-      </c>
-      <c r="C66" s="16" t="s">
-        <v>213</v>
-      </c>
-      <c r="D66" s="42" t="s">
-        <v>216</v>
       </c>
       <c r="E66" s="43" t="n">
         <v>1</v>
@@ -7181,7 +7134,7 @@
         <v>16999</v>
       </c>
       <c r="G66" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H66" s="5" t="n">
         <f aca="false">IF(G66="USD",F66*Inputs!$B$5,F66)</f>
@@ -7196,10 +7149,10 @@
         <v>No</v>
       </c>
       <c r="K66" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L66" s="16" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7207,13 +7160,13 @@
         <v>63</v>
       </c>
       <c r="B67" s="16" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C67" s="16" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="D67" s="42" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="E67" s="43" t="n">
         <v>2</v>
@@ -7222,7 +7175,7 @@
         <v>7500</v>
       </c>
       <c r="G67" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H67" s="5" t="n">
         <f aca="false">IF(G67="USD",F67*Inputs!$B$5,F67)</f>
@@ -7237,10 +7190,10 @@
         <v>No</v>
       </c>
       <c r="K67" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L67" s="16" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7248,13 +7201,13 @@
         <v>64</v>
       </c>
       <c r="B68" s="16" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C68" s="16" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="D68" s="42" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="E68" s="43" t="n">
         <v>1</v>
@@ -7263,7 +7216,7 @@
         <v>1699</v>
       </c>
       <c r="G68" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H68" s="5" t="n">
         <f aca="false">IF(G68="USD",F68*Inputs!$B$5,F68)</f>
@@ -7278,10 +7231,10 @@
         <v>No</v>
       </c>
       <c r="K68" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L68" s="16" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7289,13 +7242,13 @@
         <v>65</v>
       </c>
       <c r="B69" s="16" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C69" s="16" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="D69" s="42" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="E69" s="43" t="n">
         <v>5</v>
@@ -7304,7 +7257,7 @@
         <v>200</v>
       </c>
       <c r="G69" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H69" s="5" t="n">
         <f aca="false">IF(G69="USD",F69*Inputs!$B$5,F69)</f>
@@ -7319,10 +7272,10 @@
         <v>No</v>
       </c>
       <c r="K69" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L69" s="16" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7330,13 +7283,13 @@
         <v>66</v>
       </c>
       <c r="B70" s="36" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C70" s="36" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D70" s="37" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="E70" s="38" t="n">
         <v>20</v>
@@ -7345,7 +7298,7 @@
         <v>99</v>
       </c>
       <c r="G70" s="38" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H70" s="40" t="n">
         <f aca="false">IF(G70="USD",F70*Inputs!$B$5,F70)</f>
@@ -7360,10 +7313,10 @@
         <v>No</v>
       </c>
       <c r="K70" s="36" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L70" s="36" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7371,13 +7324,13 @@
         <v>67</v>
       </c>
       <c r="B71" s="16" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C71" s="16" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D71" s="42" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="E71" s="43" t="n">
         <v>1</v>
@@ -7386,7 +7339,7 @@
         <v>1100</v>
       </c>
       <c r="G71" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H71" s="5" t="n">
         <f aca="false">IF(G71="USD",F71*Inputs!$B$5,F71)</f>
@@ -7401,10 +7354,10 @@
         <v>No</v>
       </c>
       <c r="K71" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L71" s="16" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7412,13 +7365,13 @@
         <v>68</v>
       </c>
       <c r="B72" s="16" t="s">
+        <v>218</v>
+      </c>
+      <c r="C72" s="16" t="s">
+        <v>219</v>
+      </c>
+      <c r="D72" s="42" t="s">
         <v>222</v>
-      </c>
-      <c r="C72" s="16" t="s">
-        <v>223</v>
-      </c>
-      <c r="D72" s="42" t="s">
-        <v>226</v>
       </c>
       <c r="E72" s="43" t="n">
         <v>1</v>
@@ -7427,7 +7380,7 @@
         <v>200</v>
       </c>
       <c r="G72" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H72" s="5" t="n">
         <f aca="false">IF(G72="USD",F72*Inputs!$B$5,F72)</f>
@@ -7442,7 +7395,7 @@
         <v>No</v>
       </c>
       <c r="K72" s="16" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="L72" s="16"/>
     </row>
@@ -7451,13 +7404,13 @@
         <v>69</v>
       </c>
       <c r="B73" s="16" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C73" s="16" t="s">
+        <v>219</v>
+      </c>
+      <c r="D73" s="42" t="s">
         <v>223</v>
-      </c>
-      <c r="D73" s="42" t="s">
-        <v>227</v>
       </c>
       <c r="E73" s="43" t="n">
         <v>1</v>
@@ -7466,7 +7419,7 @@
         <v>1500</v>
       </c>
       <c r="G73" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H73" s="5" t="n">
         <f aca="false">IF(G73="USD",F73*Inputs!$B$5,F73)</f>
@@ -7481,10 +7434,10 @@
         <v>No</v>
       </c>
       <c r="K73" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L73" s="16" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7492,13 +7445,13 @@
         <v>70</v>
       </c>
       <c r="B74" s="16" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C74" s="16" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D74" s="42" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="E74" s="43" t="n">
         <v>1</v>
@@ -7507,7 +7460,7 @@
         <v>1500</v>
       </c>
       <c r="G74" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H74" s="5" t="n">
         <f aca="false">IF(G74="USD",F74*Inputs!$B$5,F74)</f>
@@ -7522,13 +7475,13 @@
         <v>No</v>
       </c>
       <c r="K74" s="16" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="L74" s="16"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D76" s="46" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="I76" s="47" t="n">
         <f aca="false">SUM(I5:I74)</f>
@@ -7537,7 +7490,7 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D77" s="48" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="I77" s="49" t="n">
         <f aca="false">SUMIF(G5:G74,"USD",I5:I74)</f>
@@ -7546,7 +7499,7 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D78" s="48" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="I78" s="48" t="str">
         <f aca="false">COUNTIF(K5:K74,"Listing")&amp;" of "&amp;COUNTA(D5:D74)</f>
@@ -7588,55 +7541,55 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="K4" s="3" t="s">
         <v>238</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C5" s="13" t="n">
         <f aca="false">COUNTIF('Baker BOM'!$B$5:$B$74,A5)</f>
@@ -7677,10 +7630,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C6" s="13" t="n">
         <f aca="false">COUNTIF('Baker BOM'!$B$5:$B$74,A6)</f>
@@ -7721,10 +7674,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C7" s="13" t="n">
         <f aca="false">COUNTIF('Baker BOM'!$B$5:$B$74,A7)</f>
@@ -7765,10 +7718,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C8" s="13" t="n">
         <f aca="false">COUNTIF('Baker BOM'!$B$5:$B$74,A8)</f>
@@ -7809,10 +7762,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C9" s="13" t="n">
         <f aca="false">COUNTIF('Baker BOM'!$B$5:$B$74,A9)</f>
@@ -7853,10 +7806,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C10" s="13" t="n">
         <f aca="false">COUNTIF('Baker BOM'!$B$5:$B$74,A10)</f>
@@ -7897,10 +7850,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C11" s="13" t="n">
         <f aca="false">COUNTIF('Baker BOM'!$B$5:$B$74,A11)</f>
@@ -7941,10 +7894,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="16" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C12" s="13" t="n">
         <f aca="false">COUNTIF('Baker BOM'!$B$5:$B$74,A12)</f>
@@ -7985,10 +7938,10 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="16" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C13" s="13" t="n">
         <f aca="false">COUNTIF('Baker BOM'!$B$5:$B$74,A13)</f>
@@ -8029,10 +7982,10 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="16" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C14" s="13" t="n">
         <f aca="false">COUNTIF('Baker BOM'!$B$5:$B$74,A14)</f>
@@ -8074,7 +8027,7 @@
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8"/>
       <c r="B15" s="8" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C15" s="8" t="n">
         <f aca="false">SUM(C5:C14)</f>
@@ -8115,7 +8068,7 @@
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="51" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="B17" s="51"/>
       <c r="C17" s="51"/>
@@ -8181,50 +8134,50 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="K4" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="L4" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8232,13 +8185,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C5" s="36" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D5" s="37" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="E5" s="38" t="n">
         <v>3</v>
@@ -8247,7 +8200,7 @@
         <v>25</v>
       </c>
       <c r="G5" s="38" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H5" s="40" t="n">
         <f aca="false">IF(G5="USD",F5*Inputs!$B$5,F5)</f>
@@ -8262,10 +8215,10 @@
         <v>Yes</v>
       </c>
       <c r="K5" s="36" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L5" s="36" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8273,13 +8226,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D6" s="42" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="E6" s="43" t="n">
         <v>3</v>
@@ -8288,7 +8241,7 @@
         <v>37</v>
       </c>
       <c r="G6" s="43" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H6" s="5" t="n">
         <f aca="false">IF(G6="USD",F6*Inputs!$B$5,F6)</f>
@@ -8303,10 +8256,10 @@
         <v>Yes</v>
       </c>
       <c r="K6" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L6" s="16" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8314,13 +8267,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="D7" s="42" t="s">
         <v>247</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>135</v>
-      </c>
-      <c r="D7" s="42" t="s">
-        <v>251</v>
       </c>
       <c r="E7" s="43" t="n">
         <v>3</v>
@@ -8329,7 +8282,7 @@
         <v>11.65</v>
       </c>
       <c r="G7" s="43" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H7" s="5" t="n">
         <f aca="false">IF(G7="USD",F7*Inputs!$B$5,F7)</f>
@@ -8344,10 +8297,10 @@
         <v>Yes</v>
       </c>
       <c r="K7" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L7" s="16" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8355,13 +8308,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D8" s="42" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="E8" s="43" t="n">
         <v>8</v>
@@ -8370,7 +8323,7 @@
         <v>8.03</v>
       </c>
       <c r="G8" s="43" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H8" s="5" t="n">
         <f aca="false">IF(G8="USD",F8*Inputs!$B$5,F8)</f>
@@ -8385,10 +8338,10 @@
         <v>Yes</v>
       </c>
       <c r="K8" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L8" s="16" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8396,13 +8349,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D9" s="42" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="E9" s="43" t="n">
         <v>2</v>
@@ -8411,7 +8364,7 @@
         <v>25</v>
       </c>
       <c r="G9" s="43" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H9" s="5" t="n">
         <f aca="false">IF(G9="USD",F9*Inputs!$B$5,F9)</f>
@@ -8426,7 +8379,7 @@
         <v>Yes</v>
       </c>
       <c r="K9" s="16" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="L9" s="16"/>
     </row>
@@ -8435,13 +8388,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="C10" s="36" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="D10" s="37" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="E10" s="38" t="n">
         <v>1</v>
@@ -8450,7 +8403,7 @@
         <v>84.38</v>
       </c>
       <c r="G10" s="38" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H10" s="40" t="n">
         <f aca="false">IF(G10="USD",F10*Inputs!$B$5,F10)</f>
@@ -8465,10 +8418,10 @@
         <v>Yes</v>
       </c>
       <c r="K10" s="36" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L10" s="36" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8476,13 +8429,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="16" t="s">
+        <v>251</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>252</v>
+      </c>
+      <c r="D11" s="42" t="s">
         <v>255</v>
-      </c>
-      <c r="C11" s="16" t="s">
-        <v>256</v>
-      </c>
-      <c r="D11" s="42" t="s">
-        <v>259</v>
       </c>
       <c r="E11" s="43" t="n">
         <v>1</v>
@@ -8491,7 +8444,7 @@
         <v>38.65</v>
       </c>
       <c r="G11" s="43" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H11" s="5" t="n">
         <f aca="false">IF(G11="USD",F11*Inputs!$B$5,F11)</f>
@@ -8506,10 +8459,10 @@
         <v>Yes</v>
       </c>
       <c r="K11" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L11" s="16" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8517,13 +8470,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="D12" s="42" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="E12" s="43" t="n">
         <v>8</v>
@@ -8532,7 +8485,7 @@
         <v>2.07</v>
       </c>
       <c r="G12" s="43" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H12" s="5" t="n">
         <f aca="false">IF(G12="USD",F12*Inputs!$B$5,F12)</f>
@@ -8547,10 +8500,10 @@
         <v>Yes</v>
       </c>
       <c r="K12" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L12" s="16" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8558,13 +8511,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="D13" s="42" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="E13" s="43" t="n">
         <v>1</v>
@@ -8573,7 +8526,7 @@
         <v>72.58</v>
       </c>
       <c r="G13" s="43" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H13" s="5" t="n">
         <f aca="false">IF(G13="USD",F13*Inputs!$B$5,F13)</f>
@@ -8588,10 +8541,10 @@
         <v>Yes</v>
       </c>
       <c r="K13" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L13" s="16" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8599,13 +8552,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="D14" s="42" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="E14" s="43" t="n">
         <v>1</v>
@@ -8614,7 +8567,7 @@
         <v>17.56</v>
       </c>
       <c r="G14" s="43" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H14" s="5" t="n">
         <f aca="false">IF(G14="USD",F14*Inputs!$B$5,F14)</f>
@@ -8629,10 +8582,10 @@
         <v>Yes</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L14" s="16" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8640,13 +8593,13 @@
         <v>11</v>
       </c>
       <c r="B15" s="36" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="C15" s="36" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="D15" s="37" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E15" s="38" t="n">
         <v>1</v>
@@ -8655,7 +8608,7 @@
         <v>85.99</v>
       </c>
       <c r="G15" s="38" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H15" s="40" t="n">
         <f aca="false">IF(G15="USD",F15*Inputs!$B$5,F15)</f>
@@ -8670,10 +8623,10 @@
         <v>Yes</v>
       </c>
       <c r="K15" s="36" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L15" s="36" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8681,13 +8634,13 @@
         <v>12</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="D16" s="42" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="E16" s="43" t="n">
         <v>1</v>
@@ -8696,7 +8649,7 @@
         <v>159</v>
       </c>
       <c r="G16" s="43" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H16" s="5" t="n">
         <f aca="false">IF(G16="USD",F16*Inputs!$B$5,F16)</f>
@@ -8711,10 +8664,10 @@
         <v>Yes</v>
       </c>
       <c r="K16" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L16" s="16" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8722,13 +8675,13 @@
         <v>13</v>
       </c>
       <c r="B17" s="36" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C17" s="36" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="D17" s="37" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="E17" s="38" t="n">
         <v>1</v>
@@ -8737,7 +8690,7 @@
         <v>110.99</v>
       </c>
       <c r="G17" s="38" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H17" s="40" t="n">
         <f aca="false">IF(G17="USD",F17*Inputs!$B$5,F17)</f>
@@ -8752,10 +8705,10 @@
         <v>Yes</v>
       </c>
       <c r="K17" s="36" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L17" s="36" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8763,13 +8716,13 @@
         <v>14</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="D18" s="42" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="E18" s="43" t="n">
         <v>1</v>
@@ -8778,7 +8731,7 @@
         <v>56.68</v>
       </c>
       <c r="G18" s="43" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H18" s="5" t="n">
         <f aca="false">IF(G18="USD",F18*Inputs!$B$5,F18)</f>
@@ -8793,10 +8746,10 @@
         <v>Yes</v>
       </c>
       <c r="K18" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L18" s="16" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8804,13 +8757,13 @@
         <v>15</v>
       </c>
       <c r="B19" s="16" t="s">
+        <v>266</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="D19" s="42" t="s">
         <v>270</v>
-      </c>
-      <c r="C19" s="16" t="s">
-        <v>271</v>
-      </c>
-      <c r="D19" s="42" t="s">
-        <v>274</v>
       </c>
       <c r="E19" s="43" t="n">
         <v>1</v>
@@ -8819,7 +8772,7 @@
         <v>40</v>
       </c>
       <c r="G19" s="43" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H19" s="5" t="n">
         <f aca="false">IF(G19="USD",F19*Inputs!$B$5,F19)</f>
@@ -8834,10 +8787,10 @@
         <v>Yes</v>
       </c>
       <c r="K19" s="16" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="L19" s="16" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8845,13 +8798,13 @@
         <v>16</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="D20" s="42" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="E20" s="43" t="n">
         <v>1</v>
@@ -8860,7 +8813,7 @@
         <v>3000</v>
       </c>
       <c r="G20" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H20" s="5" t="n">
         <f aca="false">IF(G20="USD",F20*Inputs!$B$5,F20)</f>
@@ -8875,7 +8828,7 @@
         <v>No</v>
       </c>
       <c r="K20" s="16" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="L20" s="16"/>
     </row>
@@ -8884,13 +8837,13 @@
         <v>17</v>
       </c>
       <c r="B21" s="36" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="C21" s="36" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="D21" s="37" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="E21" s="38" t="n">
         <v>1</v>
@@ -8899,7 +8852,7 @@
         <v>7500</v>
       </c>
       <c r="G21" s="38" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H21" s="40" t="n">
         <f aca="false">IF(G21="USD",F21*Inputs!$B$5,F21)</f>
@@ -8914,10 +8867,10 @@
         <v>No</v>
       </c>
       <c r="K21" s="36" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L21" s="36" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8925,13 +8878,13 @@
         <v>18</v>
       </c>
       <c r="B22" s="36" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C22" s="36" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="D22" s="37" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="E22" s="38" t="n">
         <v>1</v>
@@ -8940,7 +8893,7 @@
         <v>12000</v>
       </c>
       <c r="G22" s="38" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H22" s="40" t="n">
         <f aca="false">IF(G22="USD",F22*Inputs!$B$5,F22)</f>
@@ -8955,7 +8908,7 @@
         <v>No</v>
       </c>
       <c r="K22" s="36" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="L22" s="36"/>
     </row>
@@ -8964,13 +8917,13 @@
         <v>19</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="D23" s="42" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="E23" s="43" t="n">
         <v>1</v>
@@ -8979,7 +8932,7 @@
         <v>2500</v>
       </c>
       <c r="G23" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H23" s="5" t="n">
         <f aca="false">IF(G23="USD",F23*Inputs!$B$5,F23)</f>
@@ -8994,13 +8947,13 @@
         <v>No</v>
       </c>
       <c r="K23" s="16" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="L23" s="16"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D25" s="46" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="I25" s="47" t="n">
         <f aca="false">SUM(I5:I23)</f>
@@ -9009,7 +8962,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D26" s="48" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="I26" s="49" t="n">
         <f aca="false">SUMIF(G5:G23,"USD",I5:I23)</f>
@@ -9018,7 +8971,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D27" s="48" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="I27" s="48" t="str">
         <f aca="false">COUNTIF(K5:K23,"Listing")&amp;" of "&amp;COUNTA(D5:D23)</f>
@@ -9027,18 +8980,18 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D30" s="3" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="K30" s="3" t="s">
         <v>29</v>
@@ -9046,7 +8999,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D31" s="16" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="I31" s="7" t="n">
         <f aca="false">SUMIF($B$5:$B$23,"P1",$I$5:$I$23)</f>
@@ -9057,12 +9010,12 @@
         <v>0.203647136742268</v>
       </c>
       <c r="K31" s="18" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D32" s="16" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="I32" s="7" t="n">
         <f aca="false">SUMIF($B$5:$B$23,"P2",$I$5:$I$23)</f>
@@ -9073,12 +9026,12 @@
         <v>0.139574142199353</v>
       </c>
       <c r="K32" s="18" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D33" s="16" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="I33" s="7" t="n">
         <f aca="false">SUMIF($B$5:$B$23,"P3",$I$5:$I$23)</f>
@@ -9089,12 +9042,12 @@
         <v>0.148845466841159</v>
       </c>
       <c r="K33" s="18" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D34" s="16" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="I34" s="7" t="n">
         <f aca="false">SUMIF($B$5:$B$23,"P4",$I$5:$I$23)</f>
@@ -9105,12 +9058,12 @@
         <v>0.146883609035387</v>
       </c>
       <c r="K34" s="18" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D35" s="16" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="I35" s="7" t="n">
         <f aca="false">SUMIF($B$5:$B$23,"P5",$I$5:$I$23)</f>
@@ -9121,12 +9074,12 @@
         <v>0.0517804530662056</v>
       </c>
       <c r="K35" s="18" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D36" s="16" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="I36" s="7" t="n">
         <f aca="false">SUMIF($B$5:$B$23,"P6",$I$5:$I$23)</f>
@@ -9137,12 +9090,12 @@
         <v>0.100108875927998</v>
       </c>
       <c r="K36" s="18" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D37" s="16" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="I37" s="7" t="n">
         <f aca="false">SUMIF($G$5:$G$23,"USD",$I$5:$I$23)*Inputs!$B$8</f>
@@ -9153,12 +9106,12 @@
         <v>0.102009298642628</v>
       </c>
       <c r="K37" s="18" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D38" s="16" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="I38" s="7" t="n">
         <f aca="false">Inputs!$B$9</f>
@@ -9169,12 +9122,12 @@
         <v>0.0243022926390725</v>
       </c>
       <c r="K38" s="18" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D39" s="16" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="I39" s="7" t="n">
         <f aca="false">Inputs!$B$11</f>
@@ -9185,12 +9138,12 @@
         <v>0.082848724905929</v>
       </c>
       <c r="K39" s="18" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D40" s="8" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="I40" s="9" t="n">
         <f aca="false">SUM(I31:I39)</f>
@@ -9231,57 +9184,57 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="B6" s="5" t="n">
         <f aca="false">'Baker Cost Breakup'!E15</f>
         <v>312464.56</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="B7" s="5" t="n">
         <f aca="false">'Baker Cost Breakup'!G15</f>
         <v>12246.696</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="B8" s="7" t="n">
         <f aca="false">B6+B7</f>
@@ -9291,31 +9244,31 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="B9" s="7" t="n">
         <f aca="false">B8*Inputs!$B$7</f>
         <v>48706.6884</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="26" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="B10" s="27" t="n">
         <f aca="false">B8+B9</f>
         <v>373417.9444</v>
       </c>
       <c r="C10" s="52" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="B11" s="31" t="str">
         <f aca="false">IF(ABS(B10-'Baker Cost Breakup'!J15)&lt;1,"OK","MISMATCH")</f>
@@ -9324,7 +9277,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="B12" s="15" t="str">
         <f aca="false">COUNTIF('Baker BOM'!K5:K74,"Listing")&amp;" of "&amp;COUNTA('Baker BOM'!D5:D74)</f>
@@ -9333,12 +9286,12 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>44</v>
@@ -9349,26 +9302,26 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="16" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="B16" s="7" t="n">
         <f aca="false">B10</f>
         <v>373417.9444</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="53" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="B17" s="54" t="n">
         <f aca="false">'Baker Production (CN)'!I40</f>
         <v>144842.3016</v>
       </c>
       <c r="C17" s="52" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9380,24 +9333,24 @@
         <v>150000</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="16" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B19" s="6" t="n">
         <f aca="false">B18-B17</f>
         <v>5157.69839999999</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="16" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="B20" s="30" t="n">
         <f aca="false">IF(B18=0,0,B17/B18)</f>
@@ -9407,7 +9360,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="16" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="B21" s="7" t="n">
         <f aca="false">B16-B17</f>
@@ -9417,7 +9370,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="16" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="B22" s="30" t="n">
         <f aca="false">IF(B16=0,0,B21/B16)</f>
@@ -9427,26 +9380,26 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="16" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="B23" s="7" t="n">
         <f aca="false">B17*(1+Inputs!$B$16)</f>
         <v>159326.53176</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="16" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="B24" s="6" t="n">
         <f aca="false">B18-B23</f>
         <v>-9326.53176000001</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
     </row>
   </sheetData>
@@ -9485,50 +9438,50 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="K4" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="L4" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9536,13 +9489,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="C5" s="36" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="D5" s="37" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E5" s="38" t="n">
         <v>1</v>
@@ -9551,7 +9504,7 @@
         <v>9499</v>
       </c>
       <c r="G5" s="38" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H5" s="40" t="n">
         <f aca="false">IF(G5="USD",F5*Inputs!$B$5,F5)</f>
@@ -9566,10 +9519,10 @@
         <v>No</v>
       </c>
       <c r="K5" s="36" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L5" s="36" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9577,13 +9530,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="D6" s="42" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="E6" s="43" t="n">
         <v>2</v>
@@ -9592,7 +9545,7 @@
         <v>26.2</v>
       </c>
       <c r="G6" s="43" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H6" s="5" t="n">
         <f aca="false">IF(G6="USD",F6*Inputs!$B$5,F6)</f>
@@ -9607,10 +9560,10 @@
         <v>Yes</v>
       </c>
       <c r="K6" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L6" s="16" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9618,13 +9571,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="C7" s="16" t="s">
+        <v>333</v>
+      </c>
+      <c r="D7" s="42" t="s">
         <v>337</v>
-      </c>
-      <c r="D7" s="42" t="s">
-        <v>341</v>
       </c>
       <c r="E7" s="43" t="n">
         <v>1</v>
@@ -9633,7 +9586,7 @@
         <v>4088</v>
       </c>
       <c r="G7" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H7" s="5" t="n">
         <f aca="false">IF(G7="USD",F7*Inputs!$B$5,F7)</f>
@@ -9648,10 +9601,10 @@
         <v>No</v>
       </c>
       <c r="K7" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L7" s="16" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9659,13 +9612,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="C8" s="36" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="D8" s="37" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="E8" s="38" t="n">
         <v>4</v>
@@ -9674,7 +9627,7 @@
         <v>9</v>
       </c>
       <c r="G8" s="38" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H8" s="40" t="n">
         <f aca="false">IF(G8="USD",F8*Inputs!$B$5,F8)</f>
@@ -9689,10 +9642,10 @@
         <v>Yes</v>
       </c>
       <c r="K8" s="36" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L8" s="36" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9700,13 +9653,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="16" t="s">
+        <v>338</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>339</v>
+      </c>
+      <c r="D9" s="42" t="s">
         <v>342</v>
-      </c>
-      <c r="C9" s="16" t="s">
-        <v>343</v>
-      </c>
-      <c r="D9" s="42" t="s">
-        <v>346</v>
       </c>
       <c r="E9" s="43" t="n">
         <v>2</v>
@@ -9715,7 +9668,7 @@
         <v>0.94</v>
       </c>
       <c r="G9" s="43" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H9" s="5" t="n">
         <f aca="false">IF(G9="USD",F9*Inputs!$B$5,F9)</f>
@@ -9730,10 +9683,10 @@
         <v>Yes</v>
       </c>
       <c r="K9" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L9" s="16" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9741,13 +9694,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="C10" s="16" t="s">
+        <v>339</v>
+      </c>
+      <c r="D10" s="42" t="s">
         <v>343</v>
-      </c>
-      <c r="D10" s="42" t="s">
-        <v>347</v>
       </c>
       <c r="E10" s="43" t="n">
         <v>1</v>
@@ -9756,7 +9709,7 @@
         <v>1349</v>
       </c>
       <c r="G10" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H10" s="5" t="n">
         <f aca="false">IF(G10="USD",F10*Inputs!$B$5,F10)</f>
@@ -9771,10 +9724,10 @@
         <v>No</v>
       </c>
       <c r="K10" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L10" s="16" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9782,13 +9735,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="D11" s="42" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="E11" s="43" t="n">
         <v>1</v>
@@ -9797,7 +9750,7 @@
         <v>779</v>
       </c>
       <c r="G11" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H11" s="5" t="n">
         <f aca="false">IF(G11="USD",F11*Inputs!$B$5,F11)</f>
@@ -9812,10 +9765,10 @@
         <v>No</v>
       </c>
       <c r="K11" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L11" s="16" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9823,13 +9776,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="D12" s="42" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="E12" s="43" t="n">
         <v>2</v>
@@ -9838,7 +9791,7 @@
         <v>529</v>
       </c>
       <c r="G12" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H12" s="5" t="n">
         <f aca="false">IF(G12="USD",F12*Inputs!$B$5,F12)</f>
@@ -9853,10 +9806,10 @@
         <v>No</v>
       </c>
       <c r="K12" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L12" s="16" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9864,13 +9817,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="D13" s="42" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="E13" s="43" t="n">
         <v>2</v>
@@ -9879,7 +9832,7 @@
         <v>229</v>
       </c>
       <c r="G13" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H13" s="5" t="n">
         <f aca="false">IF(G13="USD",F13*Inputs!$B$5,F13)</f>
@@ -9894,10 +9847,10 @@
         <v>No</v>
       </c>
       <c r="K13" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L13" s="16" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9905,13 +9858,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="D14" s="42" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="E14" s="43" t="n">
         <v>8</v>
@@ -9920,7 +9873,7 @@
         <v>49</v>
       </c>
       <c r="G14" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H14" s="5" t="n">
         <f aca="false">IF(G14="USD",F14*Inputs!$B$5,F14)</f>
@@ -9935,10 +9888,10 @@
         <v>No</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L14" s="16" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9946,13 +9899,13 @@
         <v>11</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="D15" s="42" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="E15" s="43" t="n">
         <v>2</v>
@@ -9961,7 +9914,7 @@
         <v>1.49</v>
       </c>
       <c r="G15" s="43" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H15" s="5" t="n">
         <f aca="false">IF(G15="USD",F15*Inputs!$B$5,F15)</f>
@@ -9976,10 +9929,10 @@
         <v>Yes</v>
       </c>
       <c r="K15" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L15" s="16" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9987,13 +9940,13 @@
         <v>12</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="D16" s="42" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="E16" s="43" t="n">
         <v>1</v>
@@ -10002,7 +9955,7 @@
         <v>2520</v>
       </c>
       <c r="G16" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H16" s="5" t="n">
         <f aca="false">IF(G16="USD",F16*Inputs!$B$5,F16)</f>
@@ -10017,10 +9970,10 @@
         <v>No</v>
       </c>
       <c r="K16" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L16" s="16" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10028,13 +9981,13 @@
         <v>13</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="D17" s="42" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="E17" s="43" t="n">
         <v>1</v>
@@ -10043,7 +9996,7 @@
         <v>2100</v>
       </c>
       <c r="G17" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H17" s="5" t="n">
         <f aca="false">IF(G17="USD",F17*Inputs!$B$5,F17)</f>
@@ -10058,10 +10011,10 @@
         <v>No</v>
       </c>
       <c r="K17" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L17" s="16" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10069,13 +10022,13 @@
         <v>14</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="D18" s="42" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="E18" s="43" t="n">
         <v>1</v>
@@ -10084,7 +10037,7 @@
         <v>3500</v>
       </c>
       <c r="G18" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H18" s="5" t="n">
         <f aca="false">IF(G18="USD",F18*Inputs!$B$5,F18)</f>
@@ -10099,10 +10052,10 @@
         <v>No</v>
       </c>
       <c r="K18" s="16" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="L18" s="16" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10110,13 +10063,13 @@
         <v>15</v>
       </c>
       <c r="B19" s="36" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="C19" s="36" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="D19" s="37" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="E19" s="38" t="n">
         <v>1</v>
@@ -10125,7 +10078,7 @@
         <v>13409</v>
       </c>
       <c r="G19" s="38" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H19" s="40" t="n">
         <f aca="false">IF(G19="USD",F19*Inputs!$B$5,F19)</f>
@@ -10140,10 +10093,10 @@
         <v>No</v>
       </c>
       <c r="K19" s="36" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L19" s="36" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10151,13 +10104,13 @@
         <v>16</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="D20" s="42" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E20" s="43" t="n">
         <v>1</v>
@@ -10166,7 +10119,7 @@
         <v>1204</v>
       </c>
       <c r="G20" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H20" s="5" t="n">
         <f aca="false">IF(G20="USD",F20*Inputs!$B$5,F20)</f>
@@ -10181,10 +10134,10 @@
         <v>No</v>
       </c>
       <c r="K20" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L20" s="16" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10192,13 +10145,13 @@
         <v>17</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="D21" s="42" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E21" s="43" t="n">
         <v>1</v>
@@ -10207,7 +10160,7 @@
         <v>518</v>
       </c>
       <c r="G21" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H21" s="5" t="n">
         <f aca="false">IF(G21="USD",F21*Inputs!$B$5,F21)</f>
@@ -10222,10 +10175,10 @@
         <v>No</v>
       </c>
       <c r="K21" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L21" s="16" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10233,13 +10186,13 @@
         <v>18</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="D22" s="42" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="E22" s="43" t="n">
         <v>1</v>
@@ -10248,7 +10201,7 @@
         <v>1949</v>
       </c>
       <c r="G22" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H22" s="5" t="n">
         <f aca="false">IF(G22="USD",F22*Inputs!$B$5,F22)</f>
@@ -10263,10 +10216,10 @@
         <v>No</v>
       </c>
       <c r="K22" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L22" s="16" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10274,13 +10227,13 @@
         <v>19</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="D23" s="42" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E23" s="43" t="n">
         <v>1</v>
@@ -10289,7 +10242,7 @@
         <v>6799</v>
       </c>
       <c r="G23" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H23" s="5" t="n">
         <f aca="false">IF(G23="USD",F23*Inputs!$B$5,F23)</f>
@@ -10304,10 +10257,10 @@
         <v>No</v>
       </c>
       <c r="K23" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L23" s="16" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10315,13 +10268,13 @@
         <v>20</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="D24" s="42" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="E24" s="43" t="n">
         <v>4</v>
@@ -10330,7 +10283,7 @@
         <v>134</v>
       </c>
       <c r="G24" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H24" s="5" t="n">
         <f aca="false">IF(G24="USD",F24*Inputs!$B$5,F24)</f>
@@ -10345,10 +10298,10 @@
         <v>No</v>
       </c>
       <c r="K24" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L24" s="16" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10356,13 +10309,13 @@
         <v>21</v>
       </c>
       <c r="B25" s="16" t="s">
+        <v>355</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="D25" s="42" t="s">
         <v>359</v>
-      </c>
-      <c r="C25" s="16" t="s">
-        <v>360</v>
-      </c>
-      <c r="D25" s="42" t="s">
-        <v>363</v>
       </c>
       <c r="E25" s="43" t="n">
         <v>6</v>
@@ -10371,7 +10324,7 @@
         <v>19</v>
       </c>
       <c r="G25" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H25" s="5" t="n">
         <f aca="false">IF(G25="USD",F25*Inputs!$B$5,F25)</f>
@@ -10386,10 +10339,10 @@
         <v>No</v>
       </c>
       <c r="K25" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L25" s="16" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10397,13 +10350,13 @@
         <v>22</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="C26" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="D26" s="42" t="s">
         <v>360</v>
-      </c>
-      <c r="D26" s="42" t="s">
-        <v>364</v>
       </c>
       <c r="E26" s="43" t="n">
         <v>2</v>
@@ -10412,7 +10365,7 @@
         <v>899</v>
       </c>
       <c r="G26" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H26" s="5" t="n">
         <f aca="false">IF(G26="USD",F26*Inputs!$B$5,F26)</f>
@@ -10427,10 +10380,10 @@
         <v>No</v>
       </c>
       <c r="K26" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L26" s="16" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10438,13 +10391,13 @@
         <v>23</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="D27" s="42" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="E27" s="43" t="n">
         <v>1</v>
@@ -10453,7 +10406,7 @@
         <v>425</v>
       </c>
       <c r="G27" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H27" s="5" t="n">
         <f aca="false">IF(G27="USD",F27*Inputs!$B$5,F27)</f>
@@ -10468,10 +10421,10 @@
         <v>No</v>
       </c>
       <c r="K27" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L27" s="16" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10479,13 +10432,13 @@
         <v>24</v>
       </c>
       <c r="B28" s="36" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="C28" s="36" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="D28" s="37" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="E28" s="38" t="n">
         <v>1</v>
@@ -10494,7 +10447,7 @@
         <v>800</v>
       </c>
       <c r="G28" s="38" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H28" s="40" t="n">
         <f aca="false">IF(G28="USD",F28*Inputs!$B$5,F28)</f>
@@ -10509,7 +10462,7 @@
         <v>No</v>
       </c>
       <c r="K28" s="36" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="L28" s="36"/>
     </row>
@@ -10518,13 +10471,13 @@
         <v>25</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="D29" s="42" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="E29" s="43" t="n">
         <v>1</v>
@@ -10533,7 +10486,7 @@
         <v>310</v>
       </c>
       <c r="G29" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H29" s="5" t="n">
         <f aca="false">IF(G29="USD",F29*Inputs!$B$5,F29)</f>
@@ -10548,10 +10501,10 @@
         <v>No</v>
       </c>
       <c r="K29" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L29" s="16" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10559,13 +10512,13 @@
         <v>26</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="D30" s="42" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="E30" s="43" t="n">
         <v>1</v>
@@ -10574,7 +10527,7 @@
         <v>400</v>
       </c>
       <c r="G30" s="43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H30" s="5" t="n">
         <f aca="false">IF(G30="USD",F30*Inputs!$B$5,F30)</f>
@@ -10589,13 +10542,13 @@
         <v>No</v>
       </c>
       <c r="K30" s="16" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="L30" s="16"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D32" s="46" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="I32" s="47" t="n">
         <f aca="false">SUM(I5:I30)</f>
@@ -10604,7 +10557,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D33" s="48" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="I33" s="49" t="n">
         <f aca="false">SUMIF(G5:G30,"USD",I5:I30)</f>
@@ -10613,7 +10566,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D34" s="48" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="I34" s="48" t="str">
         <f aca="false">COUNTIF(K5:K30,"Listing")&amp;" of "&amp;COUNTA(D5:D30)</f>
@@ -10655,55 +10608,55 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="K4" s="3" t="s">
         <v>238</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="C5" s="13" t="n">
         <f aca="false">COUNTIF('Mixer BOM'!$B$5:$B$30,A5)</f>
@@ -10744,10 +10697,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="C6" s="13" t="n">
         <f aca="false">COUNTIF('Mixer BOM'!$B$5:$B$30,A6)</f>
@@ -10788,10 +10741,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="C7" s="13" t="n">
         <f aca="false">COUNTIF('Mixer BOM'!$B$5:$B$30,A7)</f>
@@ -10832,10 +10785,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C8" s="13" t="n">
         <f aca="false">COUNTIF('Mixer BOM'!$B$5:$B$30,A8)</f>
@@ -10877,7 +10830,7 @@
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8"/>
       <c r="B9" s="8" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="C9" s="8" t="n">
         <f aca="false">SUM(C5:C8)</f>
@@ -10918,7 +10871,7 @@
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="51" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="B11" s="51"/>
       <c r="C11" s="51"/>
@@ -10984,50 +10937,50 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="K4" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="L4" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11035,13 +10988,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="C5" s="36" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="D5" s="37" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="E5" s="38" t="n">
         <v>1</v>
@@ -11050,7 +11003,7 @@
         <v>20</v>
       </c>
       <c r="G5" s="38" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H5" s="40" t="n">
         <f aca="false">IF(G5="USD",F5*Inputs!$B$5,F5)</f>
@@ -11065,10 +11018,10 @@
         <v>Yes</v>
       </c>
       <c r="K5" s="36" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L5" s="36" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11076,13 +11029,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="16" t="s">
+        <v>371</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>372</v>
+      </c>
+      <c r="D6" s="42" t="s">
         <v>375</v>
-      </c>
-      <c r="C6" s="16" t="s">
-        <v>376</v>
-      </c>
-      <c r="D6" s="42" t="s">
-        <v>379</v>
       </c>
       <c r="E6" s="43" t="n">
         <v>1</v>
@@ -11091,7 +11044,7 @@
         <v>6.7</v>
       </c>
       <c r="G6" s="43" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H6" s="5" t="n">
         <f aca="false">IF(G6="USD",F6*Inputs!$B$5,F6)</f>
@@ -11106,10 +11059,10 @@
         <v>Yes</v>
       </c>
       <c r="K6" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L6" s="16" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11117,13 +11070,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="C7" s="16" t="s">
+        <v>372</v>
+      </c>
+      <c r="D7" s="42" t="s">
         <v>376</v>
-      </c>
-      <c r="D7" s="42" t="s">
-        <v>380</v>
       </c>
       <c r="E7" s="43" t="n">
         <v>2</v>
@@ -11132,7 +11085,7 @@
         <v>5.2</v>
       </c>
       <c r="G7" s="43" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H7" s="5" t="n">
         <f aca="false">IF(G7="USD",F7*Inputs!$B$5,F7)</f>
@@ -11147,10 +11100,10 @@
         <v>Yes</v>
       </c>
       <c r="K7" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L7" s="16" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11158,13 +11111,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="D8" s="42" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="E8" s="43" t="n">
         <v>1</v>
@@ -11173,7 +11126,7 @@
         <v>6.36</v>
       </c>
       <c r="G8" s="43" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H8" s="5" t="n">
         <f aca="false">IF(G8="USD",F8*Inputs!$B$5,F8)</f>
@@ -11188,10 +11141,10 @@
         <v>Yes</v>
       </c>
       <c r="K8" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L8" s="16" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11199,13 +11152,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="D9" s="42" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="E9" s="43" t="n">
         <v>1</v>
@@ -11214,7 +11167,7 @@
         <v>4.53</v>
       </c>
       <c r="G9" s="43" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H9" s="5" t="n">
         <f aca="false">IF(G9="USD",F9*Inputs!$B$5,F9)</f>
@@ -11229,10 +11182,10 @@
         <v>Yes</v>
       </c>
       <c r="K9" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L9" s="16" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11240,13 +11193,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="D10" s="42" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="E10" s="43" t="n">
         <v>4</v>
@@ -11255,7 +11208,7 @@
         <v>7.06</v>
       </c>
       <c r="G10" s="43" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H10" s="5" t="n">
         <f aca="false">IF(G10="USD",F10*Inputs!$B$5,F10)</f>
@@ -11270,10 +11223,10 @@
         <v>Yes</v>
       </c>
       <c r="K10" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L10" s="16" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11281,13 +11234,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="D11" s="42" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="E11" s="43" t="n">
         <v>1</v>
@@ -11296,7 +11249,7 @@
         <v>0.57</v>
       </c>
       <c r="G11" s="43" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H11" s="5" t="n">
         <f aca="false">IF(G11="USD",F11*Inputs!$B$5,F11)</f>
@@ -11311,10 +11264,10 @@
         <v>Yes</v>
       </c>
       <c r="K11" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L11" s="16" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11322,13 +11275,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="36" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="C12" s="36" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="D12" s="37" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="E12" s="38" t="n">
         <v>1</v>
@@ -11337,7 +11290,7 @@
         <v>12</v>
       </c>
       <c r="G12" s="38" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H12" s="40" t="n">
         <f aca="false">IF(G12="USD",F12*Inputs!$B$5,F12)</f>
@@ -11352,7 +11305,7 @@
         <v>Yes</v>
       </c>
       <c r="K12" s="36" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="L12" s="36"/>
     </row>
@@ -11361,13 +11314,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="D13" s="42" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="E13" s="43" t="n">
         <v>1</v>
@@ -11376,7 +11329,7 @@
         <v>8</v>
       </c>
       <c r="G13" s="43" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H13" s="5" t="n">
         <f aca="false">IF(G13="USD",F13*Inputs!$B$5,F13)</f>
@@ -11391,10 +11344,10 @@
         <v>Yes</v>
       </c>
       <c r="K13" s="16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L13" s="16" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11402,13 +11355,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="16" t="s">
+        <v>381</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>382</v>
+      </c>
+      <c r="D14" s="42" t="s">
         <v>385</v>
-      </c>
-      <c r="C14" s="16" t="s">
-        <v>386</v>
-      </c>
-      <c r="D14" s="42" t="s">
-        <v>389</v>
       </c>
       <c r="E14" s="43" t="n">
         <v>1</v>
@@ -11417,7 +11370,7 @@
         <v>4</v>
       </c>
       <c r="G14" s="43" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H14" s="5" t="n">
         <f aca="false">IF(G14="USD",F14*Inputs!$B$5,F14)</f>
@@ -11432,7 +11385,7 @@
         <v>Yes</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="L14" s="16"/>
     </row>
@@ -11441,13 +11394,13 @@
         <v>11</v>
       </c>
       <c r="B15" s="36" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="C15" s="36" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="D15" s="37" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="E15" s="38" t="n">
         <v>1</v>
@@ -11456,7 +11409,7 @@
         <v>6</v>
       </c>
       <c r="G15" s="38" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H15" s="40" t="n">
         <f aca="false">IF(G15="USD",F15*Inputs!$B$5,F15)</f>
@@ -11471,7 +11424,7 @@
         <v>Yes</v>
       </c>
       <c r="K15" s="36" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="L15" s="36"/>
     </row>
@@ -11480,13 +11433,13 @@
         <v>12</v>
       </c>
       <c r="B16" s="36" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="C16" s="36" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="D16" s="37" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="E16" s="38" t="n">
         <v>1</v>
@@ -11495,7 +11448,7 @@
         <v>6</v>
       </c>
       <c r="G16" s="38" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H16" s="40" t="n">
         <f aca="false">IF(G16="USD",F16*Inputs!$B$5,F16)</f>
@@ -11510,13 +11463,13 @@
         <v>Yes</v>
       </c>
       <c r="K16" s="36" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="L16" s="36"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D18" s="46" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="I18" s="47" t="n">
         <f aca="false">SUM(I5:I16)</f>
@@ -11525,7 +11478,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D19" s="48" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="I19" s="49" t="n">
         <f aca="false">SUMIF(G5:G16,"USD",I5:I16)</f>
@@ -11534,7 +11487,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D20" s="48" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="I20" s="48" t="str">
         <f aca="false">COUNTIF(K5:K16,"Listing")&amp;" of "&amp;COUNTA(D5:D16)</f>
@@ -11543,18 +11496,18 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D23" s="3" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>29</v>
@@ -11562,7 +11515,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D24" s="16" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="I24" s="7" t="n">
         <f aca="false">SUMIF($B$5:$B$16,"Q1",$I$5:$I$16)</f>
@@ -11573,12 +11526,12 @@
         <v>0.491868564894279</v>
       </c>
       <c r="K24" s="18" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D25" s="16" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="I25" s="7" t="n">
         <f aca="false">SUMIF($B$5:$B$16,"Q2",$I$5:$I$16)</f>
@@ -11589,12 +11542,12 @@
         <v>0.153708926529462</v>
       </c>
       <c r="K25" s="18" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D26" s="16" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="I26" s="7" t="n">
         <f aca="false">SUMIF($B$5:$B$16,"Q3",$I$5:$I$16)</f>
@@ -11605,12 +11558,12 @@
         <v>0.0384272316323655</v>
       </c>
       <c r="K26" s="18" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D27" s="16" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="I27" s="7" t="n">
         <f aca="false">SUMIF($B$5:$B$16,"Q4",$I$5:$I$16)</f>
@@ -11621,12 +11574,12 @@
         <v>0.0384272316323655</v>
       </c>
       <c r="K27" s="18" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D28" s="16" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="I28" s="7" t="n">
         <f aca="false">SUMIF($G$5:$G$16,"USD",$I$5:$I$16)*Inputs!$B$8</f>
@@ -11637,12 +11590,12 @@
         <v>0.119201272523598</v>
       </c>
       <c r="K28" s="18" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D29" s="16" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="I29" s="7" t="n">
         <f aca="false">Inputs!$B$10</f>
@@ -11653,12 +11606,12 @@
         <v>0.0128090772107885</v>
       </c>
       <c r="K29" s="18" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D30" s="16" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="I30" s="7" t="n">
         <f aca="false">Inputs!$B$12</f>
@@ -11669,12 +11622,12 @@
         <v>0.145557695577142</v>
       </c>
       <c r="K30" s="18" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D31" s="8" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="I31" s="9" t="n">
         <f aca="false">SUM(I24:I30)</f>
